--- a/content/Question Bank/Coding Questions/Unit 7 - Sets and Dictionaries/Unit 7 - Sets and Dictionaries - Coding Questions.xlsx
+++ b/content/Question Bank/Coding Questions/Unit 7 - Sets and Dictionaries/Unit 7 - Sets and Dictionaries - Coding Questions.xlsx
@@ -596,13 +596,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Read a line of space-separated numbers and print how many distinct values there are.
+          <t>The college library keeps an entry register: every time a student walks in, their roll number is logged — so the same number can appear many times in a day. The librarian wants to know how many different students actually visited, not how many entries there are.
+Read a line of space-separated numbers and print how many distinct values it contains — that is, count each value only once no matter how many times it repeats.
 ### Input Format
 - Line 1: Space-separated numbers
 ### Output Format
 ```
 3
 ```
+### Example Walkthrough
+The sample log is `1 2 2 3 3 3`. Even though there are six entries, the different values are only 1, 2 and 3, so the program prints `3`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -740,14 +743,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Read two lines of space-separated numbers and print the values that appear in both, sorted, separated by spaces.
+          <t>The music club and the drama club each keep a list of member roll numbers. For the annual day performance, the cultural secretary needs the students who belong to both clubs, since they will appear in the combined act.
+Read two lines of space-separated numbers and print the values that appear in both lines, sorted from smallest to largest, separated by spaces.
 ### Input Format
-- Line 1: First list
-- Line 2: Second list
+- Line 1: First list of numbers
+- Line 2: Second list of numbers
 ### Output Format
 ```
 3 4
 ```
+### Example Walkthrough
+The sample lists are `1 2 3 4` and `3 4 5 6`. The values present in both are 3 and 4, so the program prints `3 4`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -888,15 +894,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Build a phonebook from N entries, then look up one name. Read N, then N lines each with a name and a number, then a name to look up. Print the number, or 'Not Found' if the name is not in the book.
+          <t>The hostel warden keeps a register of student names and their room phone extensions. When a parent calls the office asking for a student, the warden wants to type the name and get the extension immediately instead of flipping through pages.
+First read `N`, then `N` lines each containing a name and a number — this builds the phonebook. Then read one more line with a name to look up. Print that person's number, or `Not Found` if the name is not in the phonebook.
 ### Input Format
-- Line 1: N
-- Next N lines: 'name number'
-- Last line: name to look up
+- Line 1: `N`, the number of entries
+- Next `N` lines: `name number`
+- Last line: the name to look up
 ### Output Format
 ```
 222
 ```
+### Example Walkthrough
+The sample phonebook has three entries: `asha 111`, `kabir 222` and `meera 333`. The name to look up is `kabir`, which is in the book with the number 222, so the program prints `222`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1062,14 +1071,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Read N items, each with a name and a price, and print the total of all the prices.
+          <t>Before the new semester, Aisha shops for stationery — a pen, a record book, a college bag — and notes each item with its price. At the counter she wants to check the shopkeeper's bill by adding up all the prices herself.
+Read `N`, then `N` lines each containing an item name and its price. Add up all the prices and print the total.
 ### Input Format
-- Line 1: N
-- Next N lines: 'name price'
+- Line 1: `N`, the number of items
+- Next `N` lines: `name price`
 ### Output Format
 ```
 260
 ```
+### Example Walkthrough
+The sample list has a pen for 10, a book for 50 and a bag for 200. Adding the prices gives 10 + 50 + 200 = 260, so the program prints `260`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1227,14 +1239,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Read two lines of space-separated numbers and print the values that are in exactly one of the two lists (not both), sorted, separated by spaces.
+          <t>Riya and Tanvi are solving the same question bank before the semester exam. Comparing notes, they want the question numbers that exactly one of them has solved — those are the ones they can explain to each other. Questions both have solved, or neither has, don't matter.
+Read two lines of space-separated numbers and print the values that appear in exactly one of the two lines (in the first or the second, but not in both), sorted from smallest to largest, separated by spaces.
 ### Input Format
-- Line 1: First list
-- Line 2: Second list
+- Line 1: First list of numbers
+- Line 2: Second list of numbers
 ### Output Format
 ```
 1 4
 ```
+### Example Walkthrough
+The sample lists are `1 2 3` and `2 3 4`. The values 2 and 3 appear in both lists, so they are dropped; 1 appears only in the first and 4 only in the second, so the program prints `1 4`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1370,15 +1385,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Read a sentence and, for each distinct word in order of first appearance, print 'word:count', one per line.
+          <t>The debate club is reviewing a member's practice speech. To spot over-used words, the club secretary wants a count of how many times each word occurs, listed in the order the words first appear in the speech.
+Read one line of text and, for each distinct word in the order of its first appearance, print `word:count` on its own line, where count is how many times that word occurs.
 ### Input Format
-- Line 1: A sentence
+- Line 1: A sentence (words separated by spaces)
 ### Output Format
 ```
 a:3
 b:2
 c:1
 ```
+### Example Walkthrough
+In the sample sentence `a b a c b a`, the word `a` occurs 3 times, `b` occurs 2 times and `c` occurs once. Listing them in order of first appearance gives the three lines `a:3`, `b:2` and `c:1`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1528,7 +1546,8 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Read a line of space-separated numbers. For each distinct number in ascending order, print 'number:square'. Build the mapping with a dictionary comprehension.
+          <t>A maths teacher is preparing a quick-reference chart of square numbers for the classroom wall. Given a rough list of numbers (possibly with repeats and in any order), the chart must show each number once, in increasing order, next to its square.
+Read a line of space-separated numbers. For each distinct number, taken in ascending order, print a line in the form `number:square`. Build the number-to-square mapping using a dictionary comprehension.
 ### Input Format
 - Line 1: Space-separated numbers
 ### Output Format
@@ -1537,6 +1556,8 @@
 2:4
 3:9
 ```
+### Example Walkthrough
+The sample input `3 1 2` contains the distinct numbers 1, 2 and 3. In ascending order their squares are 1, 4 and 9, so the program prints the lines `1:1`, `2:4` and `3:9`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1690,14 +1711,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Read N votes, each a candidate name on its own line, and print the winner (most votes). If there is a tie, print the name that comes first alphabetically.
+          <t>It is class representative election day. Each student writes one candidate's name on a slip and drops it in a box, and the class teacher counts the slips one by one. The candidate with the most votes wins; if two candidates tie, the name that comes first alphabetically is declared the winner.
+Read `N`, then `N` lines each containing one candidate name (one vote per line). Print the name of the winner — the candidate with the most votes, using alphabetical order to break any tie.
 ### Input Format
-- Line 1: N
-- Next N lines: one candidate name each
+- Line 1: `N`, the number of votes
+- Next `N` lines: one candidate name each
 ### Output Format
 ```
 asha
 ```
+### Example Walkthrough
+The sample box has 5 slips: `asha` gets 3 votes while `kabir` and `meera` get 1 each. With the most votes, `asha` wins, so the program prints `asha`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1869,16 +1893,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Read two lines of space-separated numbers. Print three lines: 'Union: X' (count of values in either set), 'Intersection: Y' (count in both), and 'Only first: Z' (count in the first but not the second).
+          <t>On sports day, the PE teacher has two sign-up sheets of student numbers — one for cricket and one for kabaddi. For the report she needs three counts: how many students signed up in total, how many signed up for both games, and how many chose only cricket.
+Read two lines of space-separated numbers. Treating each line as a set (repeats don't matter), print three lines: `Union: X` where X counts the values present in either line, `Intersection: Y` where Y counts the values present in both, and `Only first: Z` where Z counts the values in the first line but not the second.
 ### Input Format
-- Line 1: First list
-- Line 2: Second list
+- Line 1: First list of numbers
+- Line 2: Second list of numbers
 ### Output Format
 ```
 Union: 5
 Intersection: 2
 Only first: 2
 ```
+### Example Walkthrough
+The sample sets are `{1, 2, 3, 4}` and `{3, 4, 5}`. Together they contain the 5 values 1-5, the values 3 and 4 are in both, and only 1 and 2 are in the first but not the second — so the program prints `Union: 5`, `Intersection: 2` and `Only first: 2`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -2040,15 +2067,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Read N students, each with a name and a score. Using a dictionary comprehension, keep only those scoring 40 or more, and print their names sorted alphabetically, one per line.
+          <t>The exam cell is preparing the pass list after the internal test. The pass mark is 40: every student scoring 40 or more makes it onto the list, which is pinned up with the names in alphabetical order.
+Read `N`, then `N` lines each containing a student's name and score. Using a dictionary comprehension, keep only the students who scored 40 or more, and print their names in alphabetical order, one per line.
 ### Input Format
-- Line 1: N
-- Next N lines: 'name score'
+- Line 1: `N`, the number of students
+- Next `N` lines: `name score`
 ### Output Format
 ```
 asha
 meera
 ```
+### Example Walkthrough
+In the sample, `asha` scored 80 and `meera` scored 55 — both 40 or more — while `kabir` scored 30 and misses the list. Sorted alphabetically, the pass list is `asha` then `meera`, one name per line.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>

--- a/content/Question Bank/Coding Questions/Unit 7 - Sets and Dictionaries/Unit 7 - Sets and Dictionaries - Coding Questions.xlsx
+++ b/content/Question Bank/Coding Questions/Unit 7 - Sets and Dictionaries/Unit 7 - Sets and Dictionaries - Coding Questions.xlsx
@@ -1,13 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 4" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH31"/>
+  <dimension ref="A1:AH11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -621,22 +624,32 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t>sets-and-dictionaries</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>sets</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>set-operations</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -769,17 +782,27 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>sets</t>
+          <t>sets-and-dictionaries</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -921,17 +944,27 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>dictionaries</t>
+          <t>sets-and-dictionaries</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1097,17 +1130,27 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>dictionaries</t>
+          <t>sets-and-dictionaries</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1265,17 +1308,27 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>sets</t>
+          <t>sets-and-dictionaries</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1412,17 +1465,27 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>dictionaries</t>
+          <t>sets-and-dictionaries</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1573,17 +1636,27 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>dictionaries</t>
+          <t>sets-and-dictionaries</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1737,17 +1810,27 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>dictionaries</t>
+          <t>sets-and-dictionaries</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1888,10 +1971,510 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Python - Unique Count</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Unique Count. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Items
+### Output Format
+```
+3
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>sets-and-dictionaries</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>sets</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="b">
+        <v>1</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>1 2 2 3</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>a a b</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>1 1 1</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>red blue red</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>5 4 5 4 3</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>print(len(set(input().split())))</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Python - Union Words</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Union Words. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: First set
+- Line 2: Second set
+### Output Format
+```
+asha meena rohan
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>sets-and-dictionaries</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>set-operations</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="b">
+        <v>1</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>asha rohan
+meena asha</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>asha meena rohan</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>a b
+b c</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>a b c</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>x
+y</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>x y</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>same
+same</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>same</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>z y
+x z</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>x y z</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>p
+a b</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>a b p</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>m n
+q</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>m n q</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>a=set(input().split()); b=set(input().split()); print(*sorted(a|b))</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AH11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>explanation</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>difficulty</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>bloomTaxonomy</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>subjects</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>topics</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>subTopics</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>companies</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>codingType</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>supportAllLanguages</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>enablePartialScore</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>ignoreCase</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>testcase1_input</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>testcase1_output</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>testcase2_input</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>testcase2_output</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>testcase3_input</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>testcase3_output</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>testcase4_input</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>testcase4_output</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>testcase5_input</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>testcase5_output</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>testcase6_input</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>testcase6_output</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>testcase7_input</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>testcase7_output</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>preloadCode_python</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>solution_python</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>hints</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
           <t>Python - Set Report</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>On sports day, the PE teacher has two sign-up sheets of student numbers — one for cricket and one for kabaddi. For the report she needs three counts: how many students signed up in total, how many signed up for both games, and how many chose only cricket.
 Read two lines of space-separated numbers. Treating each line as a set (repeats don't matter), print three lines: `Union: X` where X counts the values present in either line, `Intersection: Y` where Y counts the values present in both, and `Only first: Z` where Z counts the values in the first line but not the second.
@@ -1911,145 +2494,155 @@
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D2" t="n">
         <v>5</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>sets</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>sets-and-dictionaries</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>set-operations</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O10" t="b">
+      <c r="O2" t="b">
         <v>0</v>
       </c>
-      <c r="P10" t="b">
+      <c r="P2" t="b">
         <v>1</v>
       </c>
-      <c r="Q10" t="b">
+      <c r="Q2" t="b">
         <v>1</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>1 2 3 4
 3 4 5</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>Union: 5
 Intersection: 2
 Only first: 2</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>1 2
 3 4</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Union: 4
 Intersection: 0
 Only first: 2</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>1 2 3
 1 2 3</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Union: 3
 Intersection: 3
 Only first: 0</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>0
 0</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Union: 1
 Intersection: 1
 Only first: 0</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>1 2 3
 4 5 6</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Union: 6
 Intersection: 0
 Only first: 3</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>-1 -2
 -2 -3</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>Union: 3
 Intersection: 1
 Only first: 1</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6 7 8
 4 5 6 7 8 9 10</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>Union: 10
 Intersection: 5
 Only first: 3</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>a = set(map(int, input().split()))
 b = set(map(int, input().split()))
@@ -2059,13 +2652,13 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Python - Passing Students</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>The exam cell is preparing the pass list after the internal test. The pass mark is 40: every student scoring 40 or more makes it onto the list, which is pinned up with the names in alphabetical order.
 Read `N`, then `N` lines each containing a student's name and score. Using a dictionary comprehension, keep only the students who scored 40 or more, and print their names in alphabetical order, one per line.
@@ -2084,54 +2677,64 @@
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D3" t="n">
         <v>5</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>dictionaries</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>sets-and-dictionaries</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
         <is>
           <t>dictionary-comprehensions</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O11" t="b">
+      <c r="O3" t="b">
         <v>0</v>
       </c>
-      <c r="P11" t="b">
+      <c r="P3" t="b">
         <v>1</v>
       </c>
-      <c r="Q11" t="b">
+      <c r="Q3" t="b">
         <v>1</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>3
 asha 80
@@ -2139,47 +2742,47 @@
 meera 55</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>asha
 meera</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>1
 sam 40</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>sam</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>2
 a 90
 b 20</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>1
 zed 39</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>4
 a 40
@@ -2188,13 +2791,13 @@
 d 0</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>a
 c</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>5
 p 41
@@ -2204,14 +2807,14 @@
 t 38</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>p
 q
 s</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>n = int(input())
 students = {}
@@ -2224,13 +2827,13 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Python - Sorted Unique</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Read a line of space-separated numbers and print each distinct value once, sorted from smallest to largest, separated by spaces.
 ### Input Format
@@ -2239,142 +2842,154 @@
 ```
 1 2 3
 ```
+### Example Walkthrough
+In the sample, the numbers are `3 1 2 1 3`. The distinct values, sorted, are `1`, `2`, and `3`, so the program prints `1 2 3`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D4" t="n">
         <v>5</v>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>sets-and-dictionaries</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t>sets</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>set-operations</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O12" t="b">
+      <c r="O4" t="b">
         <v>0</v>
       </c>
-      <c r="P12" t="b">
+      <c r="P4" t="b">
         <v>1</v>
       </c>
-      <c r="Q12" t="b">
+      <c r="Q4" t="b">
         <v>1</v>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>3 1 2 3 1</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>1 2 3</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>4 4 4 2 2</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>2 4</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>-1 -2 -1 -2</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>-2 -1</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>7 7 7 7</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6 7 8 9 10</t>
         </is>
       </c>
-      <c r="AE12" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6 7 8 9 10</t>
         </is>
       </c>
-      <c r="AG12" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>nums = list(map(int, input().split()))
 print(*sorted(set(nums)))</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Python - In Either List</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Read two lines of space-separated numbers and print all values that appear in either list, each once, sorted, separated by spaces.
 ### Input Format
@@ -2384,136 +2999,148 @@
 ```
 1 2 3
 ```
+### Example Walkthrough
+In the sample, the lists are `1 2` and `2 3`. The values in either list are `1`, `2`, and `3`, so the program prints `1 2 3`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D5" t="n">
         <v>5</v>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>sets</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>sets-and-dictionaries</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>set-operations</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O13" t="b">
+      <c r="O5" t="b">
         <v>0</v>
       </c>
-      <c r="P13" t="b">
+      <c r="P5" t="b">
         <v>1</v>
       </c>
-      <c r="Q13" t="b">
+      <c r="Q5" t="b">
         <v>1</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>1 2
 2 3</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>1 2 3</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>5
 6</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>5 6</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>1 1
 2 2</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>1 2</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>0
 0</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>1 2 3
 4 5 6</t>
         </is>
       </c>
-      <c r="AA13" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>-1 -2
 -2 -3</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>-3 -2 -1</t>
         </is>
       </c>
-      <c r="AD13" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>1 2 3 4 5
 5 6 7 8 9</t>
         </is>
       </c>
-      <c r="AE13" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6 7 8 9</t>
         </is>
       </c>
-      <c r="AG13" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>a = set(map(int, input().split()))
 b = set(map(int, input().split()))
@@ -2521,13 +3148,13 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Python - Only in the First</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Read two lines of space-separated numbers and print the values that are in the first list but not the second, sorted, separated by spaces.
 ### Input Format
@@ -2537,126 +3164,138 @@
 ```
 1 3
 ```
+### Example Walkthrough
+In the sample, the lists are `1 2 3` and `2`. Removing `2` from the first list leaves `1` and `3`, so the program prints `1 3`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="D6" t="n">
         <v>5</v>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>sets</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>sets-and-dictionaries</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>set-operations</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O14" t="b">
+      <c r="O6" t="b">
         <v>0</v>
       </c>
-      <c r="P14" t="b">
+      <c r="P6" t="b">
         <v>1</v>
       </c>
-      <c r="Q14" t="b">
+      <c r="Q6" t="b">
         <v>1</v>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>1 2 3
 2 4</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>1 3</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>5 6 7
 6</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>5 7</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>1 2 3
 4 5 6</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>1 2 3</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>0
 0</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>1 2 3
 1 2 3</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>-1 -2 -3
 -2</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>-3 -1</t>
         </is>
       </c>
-      <c r="AD14" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6 7 8
 2 4 6 8</t>
         </is>
       </c>
-      <c r="AE14" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>1 3 5 7</t>
         </is>
       </c>
-      <c r="AG14" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>a = set(map(int, input().split()))
 b = set(map(int, input().split()))
@@ -2664,15 +3303,15 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Python - Key Exists</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Read N key/value entries, then a key. Print 'Yes' if that key is present, otherwise print 'No'.
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Read `N` key/value entries, then a key. Print 'Yes' if that key is present, otherwise print 'No'.
 ### Input Format
 - Line 1: N
 - Next N lines: 'key value'
@@ -2681,59 +3320,71 @@
 ```
 Yes
 ```
+### Example Walkthrough
+In the sample, `N` is `2` with entries `a 1` and `b 2`, and the key to check is `a`. Since `a` is present, the program prints `Yes`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D7" t="n">
         <v>5</v>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>dictionaries</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>sets-and-dictionaries</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>dictionary-operations</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O15" t="b">
+      <c r="O7" t="b">
         <v>0</v>
       </c>
-      <c r="P15" t="b">
+      <c r="P7" t="b">
         <v>1</v>
       </c>
-      <c r="Q15" t="b">
+      <c r="Q7" t="b">
         <v>1</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>2
 apple 3
@@ -2741,24 +3392,24 @@
 apple</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>1
 x 1
 y</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>2
 a 1
@@ -2766,35 +3417,35 @@
 b</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>0
 z</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>1
 solo 9
 solo</t>
         </is>
       </c>
-      <c r="AA15" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>3
 a 1
@@ -2803,12 +3454,12 @@
 d</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AD15" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>4
 p 1
@@ -2818,12 +3469,12 @@
 r</t>
         </is>
       </c>
-      <c r="AE15" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AG15" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>n = int(input())
 data = {}
@@ -2835,13 +3486,13 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Python - Unique Words</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Read a sentence and print how many distinct words it contains.
 ### Input Format
@@ -2850,142 +3501,154 @@
 ```
 3
 ```
+### Example Walkthrough
+In the sample, the sentence is `a b a c`. The distinct words are `a`, `b`, and `c` - three in total - so the program prints `3`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="D8" t="n">
         <v>5</v>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>sets-and-dictionaries</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>sets</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>set-operations</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O16" t="b">
+      <c r="O8" t="b">
         <v>0</v>
       </c>
-      <c r="P16" t="b">
+      <c r="P8" t="b">
         <v>1</v>
       </c>
-      <c r="Q16" t="b">
+      <c r="Q8" t="b">
         <v>1</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>the cat the dog</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>hello</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>a a a a</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>one two three four five</t>
         </is>
       </c>
-      <c r="AA16" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>cat cat dog dog bird</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD16" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>a b a b a b a b</t>
         </is>
       </c>
-      <c r="AE16" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AG16" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>words = input().split()
 print(len(set(words)))</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Python - Set Membership</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Read a line of space-separated values, then a value. Print 'Yes' if the value is in the set of values, otherwise print 'No'.
 ### Input Format
@@ -2995,136 +3658,148 @@
 ```
 Yes
 ```
+### Example Walkthrough
+In the sample, the values are `a b c` and the value to check is `b`. Since `b` is among the values, the program prints `Yes`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D9" t="n">
         <v>5</v>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>sets-and-dictionaries</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>sets</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>set-operations</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O17" t="b">
+      <c r="O9" t="b">
         <v>0</v>
       </c>
-      <c r="P17" t="b">
+      <c r="P9" t="b">
         <v>1</v>
       </c>
-      <c r="Q17" t="b">
+      <c r="Q9" t="b">
         <v>1</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>1 2 3 4
 3</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>a b c
 z</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>5 5 5
 5</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>a
 a</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>1 2 3
 9</t>
         </is>
       </c>
-      <c r="AA17" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>x x x x
 x</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AD17" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6 7 8 9 10
 10</t>
         </is>
       </c>
-      <c r="AE17" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AG17" t="inlineStr">
+      <c r="AG9" t="inlineStr">
         <is>
           <t>values = set(input().split())
 query = input()
@@ -3132,13 +3807,544 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Python - Dictionary Lookup</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Dictionary Lookup. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: N
+- Next N lines: key value
+- Last line: key
+### Output Format
+```
+111
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>sets-and-dictionaries</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>dictionaries</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="b">
+        <v>1</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>2
+Asha 111
+Rohan 222
+Asha</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>1
+Meena 333
+Rohan</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>0
+X</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>3
+A 1
+B 2
+C 3
+C</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>1
+Z 9
+Z</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>2
+Dev 10
+Zoya 20
+Dev</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>2
+A 1
+B 2
+D</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>n=int(input()); d={}
+for _ in range(n):
+ k,v=input().split(); d[k]=v
+print(d.get(input(),"Not found"))</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Python - Value Total</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Value Total. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: N
+- Next N lines: item quantity
+### Output Format
+```
+5
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>sets-and-dictionaries</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>dictionary-operations</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="b">
+        <v>1</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>2
+pen 3
+book 2</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1
+a 10</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>3
+x 1
+y 2
+z 3</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>2
+a -1
+b 5</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>4
+p 1
+q 1
+r 1
+s 1</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>1
+only 0</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>n=int(input()); total=0
+for _ in range(n): total+=int(input().split()[1])
+print(total)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AH11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>explanation</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>difficulty</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>bloomTaxonomy</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>subjects</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>topics</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>subTopics</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>companies</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>codingType</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>supportAllLanguages</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>enablePartialScore</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>ignoreCase</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>testcase1_input</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>testcase1_output</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>testcase2_input</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>testcase2_output</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>testcase3_input</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>testcase3_output</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>testcase4_input</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>testcase4_output</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>testcase5_input</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>testcase5_output</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>testcase6_input</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>testcase6_output</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>testcase7_input</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>testcase7_output</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>preloadCode_python</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>solution_python</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>hints</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Python - Most Common Word</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Read a sentence and print the word that appears most often. If several tie, print the one that appears first.
 ### Input Format
@@ -3147,129 +4353,141 @@
 ```
 a
 ```
+### Example Walkthrough
+In the sample, the sentence is `a b a c a b`. The word `a` appears `3` times, more than any other word, so the program prints `a`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="D2" t="n">
         <v>5</v>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>dictionaries</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>sets-and-dictionaries</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>dictionary-operations</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O18" t="b">
+      <c r="O2" t="b">
         <v>0</v>
       </c>
-      <c r="P18" t="b">
+      <c r="P2" t="b">
         <v>1</v>
       </c>
-      <c r="Q18" t="b">
+      <c r="Q2" t="b">
         <v>1</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>a b a c a</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>dog cat dog cat</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>dog</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>one</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>one</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>solo</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>solo</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>x x y y y</t>
         </is>
       </c>
-      <c r="AA18" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>y</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>a b c a b c a</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="AD18" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>cat dog cat dog bird</t>
         </is>
       </c>
-      <c r="AE18" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>cat</t>
         </is>
       </c>
-      <c r="AG18" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>words = input().split()
 counts = {}
@@ -3283,13 +4501,13 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Python - Evens and Odds</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Read a line of space-separated numbers and print how many are even and how many are odd in the form 'even X odd Y'.
 ### Input Format
@@ -3298,129 +4516,141 @@
 ```
 even 2 odd 3
 ```
+### Example Walkthrough
+In the sample, the numbers are `1 2 3 4 5`. There are `2` even numbers (`2`, `4`) and `3` odd numbers (`1`, `3`, `5`), so the program prints `even 2 odd 3`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="D3" t="n">
         <v>5</v>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>dictionaries</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>sets-and-dictionaries</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
         <is>
           <t>dictionary-operations</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O19" t="b">
+      <c r="O3" t="b">
         <v>0</v>
       </c>
-      <c r="P19" t="b">
+      <c r="P3" t="b">
         <v>1</v>
       </c>
-      <c r="Q19" t="b">
+      <c r="Q3" t="b">
         <v>1</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>1 2 3 4 5</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>even 2 odd 3</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>2 4 6</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>even 3 odd 0</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>1 3 5</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>even 0 odd 3</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>even 1 odd 0</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>-2 -4 -1 -3</t>
         </is>
       </c>
-      <c r="AA19" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>even 2 odd 2</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>even 0 odd 1</t>
         </is>
       </c>
-      <c r="AD19" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6 7 8 9 10</t>
         </is>
       </c>
-      <c r="AE19" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>even 5 odd 5</t>
         </is>
       </c>
-      <c r="AG19" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>nums = list(map(int, input().split()))
 counts = {"even": 0, "odd": 0}
@@ -3433,13 +4663,13 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Python - Repeated Values</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Read a line of space-separated numbers and print the values that appear more than once, sorted, separated by spaces.
 ### Input Format
@@ -3448,119 +4678,131 @@
 ```
 2 3
 ```
+### Example Walkthrough
+In the sample, the numbers are `1 2 2 3 3`. The values `2` and `3` each appear more than once, so the program prints `2 3`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="D4" t="n">
         <v>5</v>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>dictionaries</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>sets-and-dictionaries</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t>dictionary-operations</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O20" t="b">
+      <c r="O4" t="b">
         <v>0</v>
       </c>
-      <c r="P20" t="b">
+      <c r="P4" t="b">
         <v>1</v>
       </c>
-      <c r="Q20" t="b">
+      <c r="Q4" t="b">
         <v>1</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>1 2 2 3 3 4</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>2 3</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>5 5 6 6</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>5 6</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>1 1 2 2 3</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>1 2</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>1 2 3 4 5</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>7 7 7 7 7</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AD20" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6 7 8 9 10 1 2 3</t>
         </is>
       </c>
-      <c r="AE20" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>1 2 3</t>
         </is>
       </c>
-      <c r="AG20" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>nums = list(map(int, input().split()))
 counts = {}
@@ -3571,13 +4813,13 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Python - First Unique Character</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Read a word and print the first character that appears exactly once. If every character repeats, print 'None'.
 ### Input Format
@@ -3586,129 +4828,141 @@
 ```
 c
 ```
+### Example Walkthrough
+In the sample, the word is `aabbc`. Both `a` and `b` repeat, but `c` appears only once and is the first such character, so the program prints `c`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="D5" t="n">
         <v>5</v>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>dictionaries</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>sets-and-dictionaries</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>dictionary-operations</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O21" t="b">
+      <c r="O5" t="b">
         <v>0</v>
       </c>
-      <c r="P21" t="b">
+      <c r="P5" t="b">
         <v>1</v>
       </c>
-      <c r="Q21" t="b">
+      <c r="Q5" t="b">
         <v>1</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>aabbc</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>aabb</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>xyz</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="Y21" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>aabbccd</t>
         </is>
       </c>
-      <c r="AA21" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>d</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>zzzzz</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="AD21" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>abababc</t>
         </is>
       </c>
-      <c r="AE21" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="AG21" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>word = input()
 counts = {}
@@ -3723,15 +4977,15 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Python - Merge Dictionaries</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Read a first set of key/value pairs, then a second set. Merge them so that keys in the second set overwrite the first, and print every 'key:value' with keys sorted.
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Read a first set of `N` key/value pairs, then a second set of `M` key/value pairs. Merge them so that keys in the second set overwrite the first, and print every 'key:value' with keys sorted.
 ### Input Format
 - Line 1: N
 - Next N lines: 'key value'
@@ -3742,59 +4996,71 @@
 a:1
 b:9
 ```
+### Example Walkthrough
+In the sample, the first set has `a 1` and `b 2`, and the second set has `b 9`. Merging them lets the second set's `b` overwrite the first, so the program prints `a:1` then `b:9`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D22" t="n">
+      <c r="D6" t="n">
         <v>5</v>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>dictionaries</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>sets-and-dictionaries</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>dictionary-operations</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O22" t="b">
+      <c r="O6" t="b">
         <v>0</v>
       </c>
-      <c r="P22" t="b">
+      <c r="P6" t="b">
         <v>1</v>
       </c>
-      <c r="Q22" t="b">
+      <c r="Q6" t="b">
         <v>1</v>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>2
 a 1
@@ -3803,13 +5069,13 @@
 b 9</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>a:1
 b:9</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>1
 x 5
@@ -3817,13 +5083,13 @@
 y 6</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>x:5
 y:6</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>2
 p 1
@@ -3833,31 +5099,31 @@
 q 4</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>p:3
 q:4</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>0
 0</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>1
 a 1
 0</t>
         </is>
       </c>
-      <c r="AA22" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>a:1</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>0
 2
@@ -3865,13 +5131,13 @@
 y 2</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>x:1
 y:2</t>
         </is>
       </c>
-      <c r="AD22" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>3
 a 1
@@ -3883,7 +5149,7 @@
 e 7</t>
         </is>
       </c>
-      <c r="AE22" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>a:1
 b:2
@@ -3892,7 +5158,7 @@
 e:7</t>
         </is>
       </c>
-      <c r="AG22" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>merged = {}
 n = int(input())
@@ -3908,15 +5174,15 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Python - Spending by Category</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Read N spending records, each a category and an amount. Print each category's total as 'category:total', with categories sorted alphabetically.
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Read `N` spending records, each a category and an amount. Print each category's total as 'category:total', with categories sorted alphabetically.
 ### Input Format
 - Line 1: N
 - Next N lines: 'category amount'
@@ -3925,59 +5191,71 @@
 food:130
 travel:50
 ```
+### Example Walkthrough
+In the sample, `N` is `3` with records `food 100`, `travel 50`, and `food 30`. The `food` entries total `130` and `travel` totals `50`, so the program prints `food:130` then `travel:50`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="D7" t="n">
         <v>5</v>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>dictionaries</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>sets-and-dictionaries</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>dictionary-operations</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O23" t="b">
+      <c r="O7" t="b">
         <v>0</v>
       </c>
-      <c r="P23" t="b">
+      <c r="P7" t="b">
         <v>1</v>
       </c>
-      <c r="Q23" t="b">
+      <c r="Q7" t="b">
         <v>1</v>
       </c>
-      <c r="R23" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>3
 food 100
@@ -3985,52 +5263,52 @@
 food 30</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>food:130
 travel:50</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>1
 rent 500</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>rent:500</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>2
 a 5
 a 5</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>a:10</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>1
 z 0</t>
         </is>
       </c>
-      <c r="AA23" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>z:0</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>4
 food 10
@@ -4039,14 +5317,14 @@
 bills 40</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>bills:40
 food:40
 travel:20</t>
         </is>
       </c>
-      <c r="AD23" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>5
 a 1
@@ -4056,14 +5334,14 @@
 c 5</t>
         </is>
       </c>
-      <c r="AE23" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>a:4
 b:6
 c:5</t>
         </is>
       </c>
-      <c r="AG23" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>n = int(input())
 totals = {}
@@ -4075,15 +5353,15 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Python - Student Totals</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Read N students, each on a line with a name followed by their marks. Print each student's name and total marks as 'name total', with names sorted alphabetically.
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Read `N` students, each on a line with a name followed by their marks. Print each student's name and total marks as 'name total', with names sorted alphabetically.
 ### Input Format
 - Line 1: N
 - Next N lines: 'name mark1 mark2 ...'
@@ -4092,83 +5370,95 @@
 asha 270
 kabir 180
 ```
+### Example Walkthrough
+In the sample, `N` is `2` with `asha 90 90 90` and `kabir 60 60 60`. Their totals are `270` and `180`, so the program prints `asha 270` then `kabir 180`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D24" t="n">
+      <c r="D8" t="n">
         <v>5</v>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>dictionaries</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>sets-and-dictionaries</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>dictionary-operations</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O24" t="b">
+      <c r="O8" t="b">
         <v>0</v>
       </c>
-      <c r="P24" t="b">
+      <c r="P8" t="b">
         <v>1</v>
       </c>
-      <c r="Q24" t="b">
+      <c r="Q8" t="b">
         <v>1</v>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>2
 asha 80 90 100
 kabir 70 60 50</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>asha 270
 kabir 180</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>1
 sam 40 60</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>sam 100</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>3
 c 1 2
@@ -4176,30 +5466,30 @@
 a 5 6</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>a 11
 b 7
 c 3</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>1
 solo 0 0 0</t>
         </is>
       </c>
-      <c r="AA24" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>solo 0</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>4
 zed 10
@@ -4208,7 +5498,7 @@
 beta 40</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>alpha 20
 beta 40
@@ -4216,7 +5506,7 @@
 zed 10</t>
         </is>
       </c>
-      <c r="AD24" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>5
 p 1 1
@@ -4226,7 +5516,7 @@
 t 5 5</t>
         </is>
       </c>
-      <c r="AE24" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>p 2
 q 4
@@ -4235,7 +5525,7 @@
 t 10</t>
         </is>
       </c>
-      <c r="AG24" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>n = int(input())
 totals = {}
@@ -4248,13 +5538,669 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Python - Common Names</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Common Names. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: First
+- Line 2: Second
+### Output Format
+```
+b c
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>sets-and-dictionaries</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>set-operations</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O9" t="b">
+        <v>0</v>
+      </c>
+      <c r="P9" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="b">
+        <v>1</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>a b c
+b c d</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>b c</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>x y
+z</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>same
+same</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>same</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>1 2
+2 3</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>red blue
+blue green</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>p
+a</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>m n
+n m</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>m n</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>a=set(input().split()); b=set(input().split()); print(*sorted(a&amp;b))</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Python - Character Frequency</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Character Frequency. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Text
+### Output Format
+```
+a 2
+b 1
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>sets-and-dictionaries</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>dictionary-operations</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="b">
+        <v>1</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>aba</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>a 2
+b 1</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>hello</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>e 1
+h 1
+l 2
+o 1</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>a a</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>a 2</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>x 1</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>1122</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>1 2
+2 2</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>Byte</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>B 1
+e 1
+t 1
+y 1</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>mississippi</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>i 4
+m 1
+p 2
+s 4</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>freq={}
+for ch in input():
+ if ch!=" ": freq[ch]=freq.get(ch,0)+1
+for ch in sorted(freq): print(ch, freq[ch])</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Python - Squares Dictionary</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Squares Dictionary. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: N
+### Output Format
+```
+1 4 9
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>sets-and-dictionaries</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>dictionary-comprehensions</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="b">
+        <v>1</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>1 4 9</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>1 4 9 16 25</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>1 4 9 16 25 36 49</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>1 4</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>1 4 9 16 25 36 49 64 81 100</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>n=int(input()); d={i:i*i for i in range(1,n+1)}; print(*d.values())</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AH11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>explanation</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>difficulty</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>bloomTaxonomy</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>subjects</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>topics</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>subTopics</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>companies</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>codingType</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>supportAllLanguages</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>enablePartialScore</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>ignoreCase</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>testcase1_input</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>testcase1_output</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>testcase2_input</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>testcase2_output</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>testcase3_input</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>testcase3_output</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>testcase4_input</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>testcase4_output</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>testcase5_input</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>testcase5_output</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>testcase6_input</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>testcase6_output</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>testcase7_input</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>testcase7_output</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>preloadCode_python</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>solution_python</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>hints</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Python - Word Count Ranking</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Read a sentence and print each distinct word with its count as 'word count', ordered by count from highest to lowest. Break ties alphabetically.
 ### Input Format
@@ -4265,140 +6211,152 @@
 b 2
 c 1
 ```
+### Example Walkthrough
+In the sample, the sentence is `a b a c a b`. The word `a` appears `3` times, `b` appears `2` times, and `c` appears `1` time, so the program prints `a 3`, `b 2`, and `c 1` in that order.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D25" t="n">
+      <c r="D2" t="n">
         <v>5</v>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>dictionaries</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>sets-and-dictionaries</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>dictionary-operations</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O25" t="b">
+      <c r="O2" t="b">
         <v>0</v>
       </c>
-      <c r="P25" t="b">
+      <c r="P2" t="b">
         <v>1</v>
       </c>
-      <c r="Q25" t="b">
+      <c r="Q2" t="b">
         <v>1</v>
       </c>
-      <c r="R25" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>a b a c b a</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>a 3
 b 2
 c 1</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>dog cat dog</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>dog 2
 cat 1</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>x y z</t>
         </is>
       </c>
-      <c r="W25" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>x 1
 y 1
 z 1</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>solo</t>
         </is>
       </c>
-      <c r="Y25" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>solo 1</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>a a b b c c</t>
         </is>
       </c>
-      <c r="AA25" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>a 2
 b 2
 c 2</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>z y x z y z</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>z 3
 y 2
 x 1</t>
         </is>
       </c>
-      <c r="AD25" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>one two two three three three</t>
         </is>
       </c>
-      <c r="AE25" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>three 3
 two 2
 one 1</t>
         </is>
       </c>
-      <c r="AG25" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>words = input().split()
 counts = {}
@@ -4409,13 +6367,13 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Python - Character Frequency Ranking</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Read a word and print each character with its count as 'char:count', ordered by count from highest to lowest, breaking ties alphabetically.
 ### Input Format
@@ -4427,64 +6385,76 @@
 h:1
 o:1
 ```
+### Example Walkthrough
+In the sample, the word is `hello`. The letter `l` appears twice, more than any other character, so it is printed first as `l:2`, followed by the remaining letters `e`, `h`, and `o` (each appearing once) in alphabetical order.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D26" t="n">
+      <c r="D3" t="n">
         <v>5</v>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>dictionaries</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>sets-and-dictionaries</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
         <is>
           <t>dictionary-operations</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O26" t="b">
+      <c r="O3" t="b">
         <v>0</v>
       </c>
-      <c r="P26" t="b">
+      <c r="P3" t="b">
         <v>1</v>
       </c>
-      <c r="Q26" t="b">
+      <c r="Q3" t="b">
         <v>1</v>
       </c>
-      <c r="R26" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>hello</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>l:2
 e:1
@@ -4492,24 +6462,24 @@
 o:1</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>aabbcc</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>a:2
 b:2
 c:2</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>mississippi</t>
         </is>
       </c>
-      <c r="W26" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>i:4
 s:4
@@ -4517,53 +6487,53 @@
 m:1</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="Y26" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>a:1</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>zzzzyyyxx</t>
         </is>
       </c>
-      <c r="AA26" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>z:4
 y:3
 x:2</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>abcabcabc</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>a:3
 b:3
 c:3</t>
         </is>
       </c>
-      <c r="AD26" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>banana</t>
         </is>
       </c>
-      <c r="AE26" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>a:3
 n:2
 b:1</t>
         </is>
       </c>
-      <c r="AG26" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>word = input()
 counts = {}
@@ -4574,13 +6544,13 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Python - Group by Length</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Read a sentence and group its words by length. For each length in ascending order, print 'length: ' followed by the words of that length in order of appearance, separated by spaces.
 ### Input Format
@@ -4591,117 +6561,129 @@
 3: cat dog
 4: fish bird
 ```
+### Example Walkthrough
+In the sample, the sentence is `a cat dog fish bird`. Grouped by length, `a` has length `1`, `cat` and `dog` have length `3`, and `fish` and `bird` have length `4`, so the program prints `1: a`, `3: cat dog`, and `4: fish bird`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D27" t="n">
+      <c r="D4" t="n">
         <v>5</v>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>dictionaries</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>sets-and-dictionaries</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t>dictionary-operations</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O27" t="b">
+      <c r="O4" t="b">
         <v>0</v>
       </c>
-      <c r="P27" t="b">
+      <c r="P4" t="b">
         <v>1</v>
       </c>
-      <c r="Q27" t="b">
+      <c r="Q4" t="b">
         <v>1</v>
       </c>
-      <c r="R27" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>cat dog fish bird a</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>1: a
 3: cat dog
 4: fish bird</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>hi hey</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>2: hi
 3: hey</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>one two six</t>
         </is>
       </c>
-      <c r="W27" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>3: one two six</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="Y27" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>1: x</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>aa bb cc</t>
         </is>
       </c>
-      <c r="AA27" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>2: aa bb cc</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>a bb ccc dddd eeeee</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>1: a
 2: bb
@@ -4710,17 +6692,17 @@
 5: eeeee</t>
         </is>
       </c>
-      <c r="AD27" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>cat bat hat mat sat pat</t>
         </is>
       </c>
-      <c r="AE27" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>3: cat bat hat mat sat pat</t>
         </is>
       </c>
-      <c r="AG27" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>words = input().split()
 groups = {}
@@ -4731,15 +6713,15 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Python - Common Keys Summed</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Read two dictionaries of 'key value' pairs. For each key present in both, print 'key:sum' where sum adds the two values, with keys sorted alphabetically.
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Read two dictionaries of 'key value' pairs, sized `N` and `M`. For each key present in both, print 'key:sum' where sum adds the two values, with keys sorted alphabetically.
 ### Input Format
 - Line 1: N
 - Next N lines: 'key value'
@@ -4749,59 +6731,71 @@
 ```
 b:5
 ```
+### Example Walkthrough
+In the sample, the first dictionary has `a 1` and `b 2`, and the second has `b 3` and `c 4`. Only `b` is present in both, summing to `2 + 3 = 5`, so the program prints `b:5`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D28" t="n">
+      <c r="D5" t="n">
         <v>5</v>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>dictionaries</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>sets-and-dictionaries</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>dictionary-operations</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O28" t="b">
+      <c r="O5" t="b">
         <v>0</v>
       </c>
-      <c r="P28" t="b">
+      <c r="P5" t="b">
         <v>1</v>
       </c>
-      <c r="Q28" t="b">
+      <c r="Q5" t="b">
         <v>1</v>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>2
 a 1
@@ -4811,12 +6805,12 @@
 c 4</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>b:5</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>1
 x 5
@@ -4824,12 +6818,12 @@
 x 10</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>x:15</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>2
 p 1
@@ -4838,32 +6832,32 @@
 q 8</t>
         </is>
       </c>
-      <c r="W28" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>q:10</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>0
 0</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>1
 a 1
 0</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>0
 1
 x 5</t>
         </is>
       </c>
-      <c r="AD28" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>3
 a 1
@@ -4875,14 +6869,14 @@
 c 30</t>
         </is>
       </c>
-      <c r="AE28" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>a:11
 b:22
 c:33</t>
         </is>
       </c>
-      <c r="AG28" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>first = {}
 n = int(input())
@@ -4900,13 +6894,13 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Python - Majority Element</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Read a line of space-separated numbers and print the value that appears more than half the time. If no value has a strict majority, print 'None'.
 ### Input Format
@@ -4915,129 +6909,141 @@
 ```
 1
 ```
+### Example Walkthrough
+In the sample, the numbers are `1 1 1 2 3`. The value `1` appears `3` times out of `5`, more than half, so the program prints `1`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="D6" t="n">
         <v>5</v>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>dictionaries</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>sets-and-dictionaries</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>dictionary-operations</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O29" t="b">
+      <c r="O6" t="b">
         <v>0</v>
       </c>
-      <c r="P29" t="b">
+      <c r="P6" t="b">
         <v>1</v>
       </c>
-      <c r="Q29" t="b">
+      <c r="Q6" t="b">
         <v>1</v>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>1 1 1 2 3</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>1 2 3 4</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>2 2 2 2</t>
         </is>
       </c>
-      <c r="W29" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Y29" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>1 1 2 2 3</t>
         </is>
       </c>
-      <c r="AA29" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>-1 -1 -1 -2</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="AD29" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>1 1 1 1 1 2 2 2 3 3</t>
         </is>
       </c>
-      <c r="AE29" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="AG29" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>nums = list(map(int, input().split()))
 counts = {}
@@ -5051,15 +7057,15 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Python - Count Anagram Groups</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Read N words and print how many distinct anagram groups they form (words are in the same group if they use the same letters).
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Read `N` words and print how many distinct anagram groups they form (words are in the same group if they use the same letters).
 ### Input Format
 - Line 1: N
 - Next N lines: one word each
@@ -5067,59 +7073,71 @@
 ```
 2
 ```
+### Example Walkthrough
+In the sample, `N` is `3` with the words `cat`, `act`, and `dog`. `cat` and `act` use the same letters and form one group, while `dog` forms another, so the program prints `2`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D30" t="n">
+      <c r="D7" t="n">
         <v>5</v>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>dictionaries</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>set-operations</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>sets-and-dictionaries</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>sets</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O30" t="b">
+      <c r="O7" t="b">
         <v>0</v>
       </c>
-      <c r="P30" t="b">
+      <c r="P7" t="b">
         <v>1</v>
       </c>
-      <c r="Q30" t="b">
+      <c r="Q7" t="b">
         <v>1</v>
       </c>
-      <c r="R30" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>3
 listen
@@ -5127,24 +7145,24 @@
 hello</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>2
 abc
 cba</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>3
 cat
@@ -5152,33 +7170,33 @@
 bird</t>
         </is>
       </c>
-      <c r="W30" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y30" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>1
 solo</t>
         </is>
       </c>
-      <c r="AA30" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>4
 abc
@@ -5187,12 +7205,12 @@
 xyz</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AD30" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>5
 rat
@@ -5202,12 +7220,12 @@
 arc</t>
         </is>
       </c>
-      <c r="AE30" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AG30" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>n = int(input())
 groups = set()
@@ -5218,15 +7236,15 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Python - Top Customer</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Read N transactions, each a customer name and an amount. Print the customer with the highest total spend. If several tie, print the name that comes first alphabetically.
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Read `N` transactions, each a customer name and an amount. Print the customer with the highest total spend. If several tie, print the name that comes first alphabetically.
 ### Input Format
 - Line 1: N
 - Next N lines: 'name amount'
@@ -5234,59 +7252,71 @@
 ```
 asha
 ```
+### Example Walkthrough
+In the sample, `N` is `3` with `asha 100`, `kabir 50`, and `asha 80`. `asha`'s total is `100 + 80 = 180`, more than `kabir`'s `50`, so the program prints `asha`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D31" t="n">
+      <c r="D8" t="n">
         <v>5</v>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>dictionaries</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>sets-and-dictionaries</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>dictionary-operations</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O31" t="b">
+      <c r="O8" t="b">
         <v>0</v>
       </c>
-      <c r="P31" t="b">
+      <c r="P8" t="b">
         <v>1</v>
       </c>
-      <c r="Q31" t="b">
+      <c r="Q8" t="b">
         <v>1</v>
       </c>
-      <c r="R31" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>4
 asha 100
@@ -5295,23 +7325,23 @@
 kabir 50</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>asha</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>1
 sam 5</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>sam</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>3
 a 10
@@ -5319,35 +7349,35 @@
 a 25</t>
         </is>
       </c>
-      <c r="W31" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>1
 solo 0</t>
         </is>
       </c>
-      <c r="Y31" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>solo</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>2
 a 0
 b 0</t>
         </is>
       </c>
-      <c r="AA31" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>4
 x 10
@@ -5356,12 +7386,12 @@
 x 0</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="AD31" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>5
 p 100
@@ -5371,12 +7401,12 @@
 q 0</t>
         </is>
       </c>
-      <c r="AE31" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>p</t>
         </is>
       </c>
-      <c r="AG31" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>n = int(input())
 totals = {}
@@ -5389,6 +7419,527 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Python - Nested Marks Average</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Nested Marks Average. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: N
+- Next N lines: name mark1 mark2
+- Last line: name
+### Output Format
+```
+85.0
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>sets-and-dictionaries</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>nested-dictionaries</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O9" t="b">
+        <v>0</v>
+      </c>
+      <c r="P9" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="b">
+        <v>1</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>2
+Asha 80 90
+Rohan 70 75
+Asha</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>1
+Meena 100 50
+Meena</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>2
+A 1 3
+B 2 4
+B</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>1
+X 0 0
+Y</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>3
+D 10 20
+E 30 40
+F 50 60
+F</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>2
+P -10 10
+Q 5 5
+P</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>1
+S 99 100
+S</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>99.5</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>n=int(input()); data={}
+for _ in range(n):
+ name,m1,m2=input().split(); data[name]={"m1":int(m1),"m2":int(m2)}
+t=input(); print((data[t]["m1"]+data[t]["m2"])/2 if t in data else "Not found")</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Python - Invert Dictionary</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Invert Dictionary. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: N
+- Next N lines: key value
+### Output Format
+```
+1:a
+2:b
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>sets-and-dictionaries</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>dictionary-operations</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="b">
+        <v>1</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>2
+a 1
+b 2</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>1:a
+2:b</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>1
+x y</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>y:x</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>3
+a red
+b blue
+c green</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>blue:b
+green:c
+red:a</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>2
+name Asha
+city Pune</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Asha:name
+Pune:city</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>2
+a 1
+b 1</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>1:b</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>4
+w 4
+x 3
+y 2
+z 1</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>1:z
+2:y
+3:x
+4:w</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>n=int(input()); d={}
+for _ in range(n):
+ k,v=input().split(); d[v]=k
+for v in sorted(d): print(f"{v}:{d[v]}")</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Python - Membership Queries</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Membership Queries. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Stored items
+- Line 2: Queries
+### Output Format
+```
+Yes
+No
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>sets-and-dictionaries</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>choosing-data-structures</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="b">
+        <v>1</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>a b c
+a d</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Yes
+No</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1 2 3
+3 4</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Yes
+No</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>x
+x</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>red blue
+green red</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>No
+Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>p
+a</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>p q
+q p r</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Yes
+Yes
+No</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>5 5
+5 6</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>Yes
+No</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>stored=set(input().split())
+for q in input().split(): print("Yes" if q in stored else "No")</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/content/Question Bank/Coding Questions/Unit 7 - Sets and Dictionaries/Unit 7 - Sets and Dictionaries - Coding Questions.xlsx
+++ b/content/Question Bank/Coding Questions/Unit 7 - Sets and Dictionaries/Unit 7 - Sets and Dictionaries - Coding Questions.xlsx
@@ -1976,16 +1976,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Unique Count. Read the input values and print the required result exactly.
+          <t>A quiz show logs the answer submitted by each contestant during a round, and popular answers are often repeated by many contestants. The host wants to know how many genuinely different answers were given, not how many contestants answered.
+Write a program that reads a line of space-separated words and prints how many distinct words it contains, counting each different word only once.
 ### Input Format
-- Line 1: Items
+- Line 1: Space-separated words
 ### Output Format
 ```
 3
 ```
+### Example Walkthrough
+In the sample, the answers are `1 2 2 3`. Even though there are four entries, the different values are only 1, 2, and 3, so the program prints `3`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- The input line has at least one value.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -2129,17 +2132,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Union Words. Read the input values and print the required result exactly.
+          <t>Two class representatives each submit a guest list of names invited to a joint event, and the organizer needs a single combined guest list with every name that appears on either list, with no repeats, in alphabetical order.
+Write a program that reads two lines of space-separated names and prints every name that appears in at least one of the two lists, sorted alphabetically and separated by single spaces, with no duplicates.
 ### Input Format
-- Line 1: First set
-- Line 2: Second set
+- Line 1: Space-separated names (first list)
+- Line 2: Space-separated names (second list)
 ### Output Format
 ```
 asha meena rohan
 ```
+### Example Walkthrough
+In the sample, the first list is `asha rohan` and the second is `meena asha`. Combining both lists and removing the repeated `asha` gives `asha`, `meena`, and `rohan`, which sorted alphabetically prints as `asha meena rohan`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- The inputs are valid lines of space-separated names.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -3815,18 +3821,21 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Dictionary Lookup. Read the input values and print the required result exactly.
+          <t>A hostel's key-card office keeps a lookup table mapping each resident's name to their card ID. When a resident's name is queried at the front desk, the system needs to report the matching card ID, or say the name isn't registered.
+Write a program that reads a whole number N, then reads N lines each with a name and an ID separated by a space and stores them in a dictionary, then reads one more name and prints its ID if it exists in the dictionary, or `Not found` otherwise.
 ### Input Format
-- Line 1: N
-- Next N lines: key value
-- Last line: key
+- Line 1: N, the number of registered residents
+- Next N lines: name and ID separated by a space
+- Final line: the name being queried
 ### Output Format
 ```
 111
 ```
+### Example Walkthrough
+In the sample, N is 2 with `Asha 111` and `Rohan 222` registered, and the query is `Asha`. Since Asha is in the dictionary with ID `111`, the program prints `111`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- Names and IDs are valid strings with no spaces within them.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -3991,17 +4000,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Value Total. Read the input values and print the required result exactly.
+          <t>A canteen till reads a list of item names and prices punched in one per line during the day and needs the total bill amount collected across all of them.
+Write a program that reads a whole number N, then reads N lines each with an item name and a price separated by a space, and prints the sum of all the prices.
 ### Input Format
-- Line 1: N
-- Next N lines: item quantity
+- Line 1: N, the number of items
+- Next N lines: item name and price separated by a space
 ### Output Format
 ```
 5
 ```
+### Example Walkthrough
+In the sample, N is 2 with `pen 3` and `book 2`. Adding the prices 3 and 2 gives 5, so the program prints `5`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- Item names contain no spaces, and prices are valid whole numbers.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -5546,17 +5558,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Common Names. Read the input values and print the required result exactly.
+          <t>Two hostel wardens each keep a guest list for the weekend, and the security desk needs to know which names appear on both lists, since those visitors need double clearance.
+Write a program that reads two lines of space-separated names and prints only the names that appear in both lists, sorted alphabetically and separated by single spaces. If no name appears on both lists, print an empty line.
 ### Input Format
-- Line 1: First
-- Line 2: Second
+- Line 1: Space-separated names (first warden's list)
+- Line 2: Space-separated names (second warden's list)
 ### Output Format
 ```
 b c
 ```
+### Example Walkthrough
+In the sample, the first list is `a b c` and the second is `b c d`. The names appearing on both lists are `b` and `c`, so the program prints `b c`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- The inputs are valid lines of space-separated names.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -5633,7 +5648,6 @@
 z</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
           <t>same
@@ -5673,7 +5687,6 @@
 a</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
           <t>m n
@@ -5699,17 +5712,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Character Frequency. Read the input values and print the required result exactly.
+          <t>A typing-speed app analyzes a practice sentence a student typed and reports how many times each character was used (ignoring spaces), sorted alphabetically, to spot which keys need the most practice.
+Write a program that reads a line of text and, for every distinct character other than a space, prints that character and how many times it appears, one per line in the form `&lt;character&gt; &lt;count&gt;`, sorted alphabetically by character.
 ### Input Format
-- Line 1: Text
+- Line 1: A line of text
 ### Output Format
 ```
 a 2
 b 1
 ```
+### Example Walkthrough
+In the sample, the text is `aba`. The character `a` appears 2 times and `b` appears 1 time, so the program prints `a 2` then `b 1` in alphabetical order.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- The input is a valid line of text.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -5867,16 +5883,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Squares Dictionary. Read the input values and print the required result exactly.
+          <t>A number-pattern app for young learners builds a table mapping every number from 1 to N to its square, then shows the squares in order to help students spot the pattern.
+Write a program that reads a whole number N, builds a dictionary mapping each number from 1 to N to its square, and prints just the square values in order, separated by single spaces. If N is 0, print an empty line.
 ### Input Format
 - Line 1: N
 ### Output Format
 ```
 1 4 9
 ```
+### Example Walkthrough
+In the sample, N is 3. The dictionary maps 1 to 1, 2 to 4, and 3 to 9, and printing the values in order gives `1 4 9`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- All numeric inputs are valid whole numbers in the ranges implied by the examples.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -5961,7 +5980,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
           <t>5</t>
@@ -7427,18 +7445,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Nested Marks Average. Read the input values and print the required result exactly.
+          <t>A report-card generator stores each student's marks in two tests inside a dictionary of dictionaries, keyed first by student name. When a name is queried, it prints that student's average of the two test marks, or `Not found` if the student wasn't recorded.
+Write a program that reads a whole number N, then reads N lines each with a name and two test marks separated by spaces and stores them in a nested dictionary, then reads one more name and prints the average of that student's two marks if found, or `Not found` otherwise.
 ### Input Format
-- Line 1: N
-- Next N lines: name mark1 mark2
-- Last line: name
+- Line 1: N, the number of students
+- Next N lines: name, first mark, and second mark separated by spaces
+- Final line: the name being queried
 ### Output Format
 ```
 85.0
 ```
+### Example Walkthrough
+In the sample, N is 2 with `Asha 80 90` and `Rohan 70 75` recorded, and the query is `Asha`. Asha's average is (80 + 90) / 2 = 85.0, so the program prints `85.0`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- Names contain no spaces, and marks are valid whole numbers.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -7604,18 +7625,21 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Invert Dictionary. Read the input values and print the required result exactly.
+          <t>A gift-shop inventory system stores each item's code mapped to its name. For a reverse-lookup screen, the system needs an inverted table that maps each name back to its code, sorted alphabetically by name. If two items share the same name, the code from the later entry overwrites the earlier one.
+Write a program that reads a whole number N, then reads N lines each with a code and a name separated by a space, builds an inverted dictionary mapping name to code, and prints each entry sorted alphabetically by name in the form `&lt;name&gt;:&lt;code&gt;`.
 ### Input Format
-- Line 1: N
-- Next N lines: key value
+- Line 1: N, the number of items
+- Next N lines: code and name separated by a space
 ### Output Format
 ```
 1:a
 2:b
 ```
+### Example Walkthrough
+In the sample, N is 2 with `a 1` and `b 2`. Inverting gives `1` mapped to `a` and `2` mapped to `b`, and printing them sorted by name gives `1:a` then `2:b`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- Codes and names contain no spaces within them.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -7719,7 +7743,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr">
         <is>
           <t>2
@@ -7779,18 +7802,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Membership Queries. Read the input values and print the required result exactly.
+          <t>An event check-in system keeps a set of names on the guest list. As people arrive one by one, the desk types out each visitor's name and needs an instant `Yes` or `No` for whether they're on the list.
+Write a program that reads a line of space-separated names into a set (the guest list), then reads a second line of space-separated names to check, and for each name checked prints `Yes` if it is in the guest list, or `No` otherwise, one result per line in the order checked.
 ### Input Format
-- Line 1: Stored items
-- Line 2: Queries
+- Line 1: Space-separated names (the guest list)
+- Line 2: Space-separated names (the names to check)
 ### Output Format
 ```
 Yes
 No
 ```
+### Example Walkthrough
+In the sample, the guest list is `a b c` and the names to check are `a d`. `a` is on the list, so it prints `Yes`; `d` is not, so it prints `No`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- The inputs are valid lines of space-separated names.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D11" t="n">

--- a/content/Question Bank/Coding Questions/Unit 7 - Sets and Dictionaries/Unit 7 - Sets and Dictionaries - Coding Questions.xlsx
+++ b/content/Question Bank/Coding Questions/Unit 7 - Sets and Dictionaries/Unit 7 - Sets and Dictionaries - Coding Questions.xlsx
@@ -7,10 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 3" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 4" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - Coding - Unit 7" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH11"/>
+  <dimension ref="A1:AH41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -601,17 +598,11 @@
         <is>
           <t>The college library keeps an entry register: every time a student walks in, their roll number is logged — so the same number can appear many times in a day. The librarian wants to know how many different students actually visited, not how many entries there are.
 Read a line of space-separated numbers and print how many distinct values it contains — that is, count each value only once no matter how many times it repeats.
-### Input Format
-- Line 1: Space-separated numbers
-### Output Format
-```
-3
-```
 ### Example Walkthrough
 The sample log is `1 2 2 3 3 3`. Even though there are six entries, the different values are only 1, 2 and 3, so the program prints `3`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -744,7 +735,7 @@
       <c r="AG2" t="inlineStr">
         <is>
           <t>nums = input().split()
-print(len(set(nums)))</t>
+print(len(set(nums)))   # set keeps only unique values, so len gives distinct count</t>
         </is>
       </c>
     </row>
@@ -758,18 +749,11 @@
         <is>
           <t>The music club and the drama club each keep a list of member roll numbers. For the annual day performance, the cultural secretary needs the students who belong to both clubs, since they will appear in the combined act.
 Read two lines of space-separated numbers and print the values that appear in both lines, sorted from smallest to largest, separated by spaces.
-### Input Format
-- Line 1: First list of numbers
-- Line 2: Second list of numbers
-### Output Format
-```
-3 4
-```
 ### Example Walkthrough
 The sample lists are `1 2 3 4` and `3 4 5 6`. The values present in both are 3 and 4, so the program prints `3 4`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -905,7 +889,7 @@
         <is>
           <t>a = set(map(int, input().split()))
 b = set(map(int, input().split()))
-print(*sorted(a &amp; b))</t>
+print(*sorted(a &amp; b))   # &amp; keeps only values common to both sets</t>
         </is>
       </c>
     </row>
@@ -919,19 +903,11 @@
         <is>
           <t>The hostel warden keeps a register of student names and their room phone extensions. When a parent calls the office asking for a student, the warden wants to type the name and get the extension immediately instead of flipping through pages.
 First read `N`, then `N` lines each containing a name and a number — this builds the phonebook. Then read one more line with a name to look up. Print that person's number, or `Not Found` if the name is not in the phonebook.
-### Input Format
-- Line 1: `N`, the number of entries
-- Next `N` lines: `name number`
-- Last line: the name to look up
-### Output Format
-```
-222
-```
 ### Example Walkthrough
 The sample phonebook has three entries: `asha 111`, `kabir 222` and `meera 333`. The name to look up is `kabir`, which is in the book with the number 222, so the program prints `222`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -1090,9 +1066,9 @@
 book = {}
 for _ in range(n):
     name, number = input().split()
-    book[name] = number
+    book[name] = number   # store each name as a key mapped to its number
 query = input()
-print(book.get(query, "Not Found"))</t>
+print(book.get(query, "Not Found"))   # get() avoids an error if the name is missing</t>
         </is>
       </c>
     </row>
@@ -1106,18 +1082,11 @@
         <is>
           <t>Before the new semester, Aisha shops for stationery — a pen, a record book, a college bag — and notes each item with its price. At the counter she wants to check the shopkeeper's bill by adding up all the prices herself.
 Read `N`, then `N` lines each containing an item name and its price. Add up all the prices and print the total.
-### Input Format
-- Line 1: `N`, the number of items
-- Next `N` lines: `name price`
-### Output Format
-```
-260
-```
 ### Example Walkthrough
 The sample list has a pen for 10, a book for 50 and a bag for 200. Adding the prices gives 10 + 50 + 200 = 260, so the program prints `260`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -1269,8 +1238,8 @@
 prices = {}
 for _ in range(n):
     name, price = input().split()
-    prices[name] = int(price)
-print(sum(prices.values()))</t>
+    prices[name] = int(price)   # convert price to int before storing
+print(sum(prices.values()))   # sum just the values, ignoring the item names</t>
         </is>
       </c>
     </row>
@@ -1284,18 +1253,11 @@
         <is>
           <t>Riya and Tanvi are solving the same question bank before the semester exam. Comparing notes, they want the question numbers that exactly one of them has solved — those are the ones they can explain to each other. Questions both have solved, or neither has, don't matter.
 Read two lines of space-separated numbers and print the values that appear in exactly one of the two lines (in the first or the second, but not in both), sorted from smallest to largest, separated by spaces.
-### Input Format
-- Line 1: First list of numbers
-- Line 2: Second list of numbers
-### Output Format
-```
-1 4
-```
 ### Example Walkthrough
 The sample lists are `1 2 3` and `2 3 4`. The values 2 and 3 appear in both lists, so they are dropped; 1 appears only in the first and 4 only in the second, so the program prints `1 4`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -1426,7 +1388,7 @@
         <is>
           <t>a = set(map(int, input().split()))
 b = set(map(int, input().split()))
-print(*sorted(a ^ b))</t>
+print(*sorted(a ^ b))   # ^ keeps values that are in exactly one of the two sets</t>
         </is>
       </c>
     </row>
@@ -1440,19 +1402,11 @@
         <is>
           <t>The debate club is reviewing a member's practice speech. To spot over-used words, the club secretary wants a count of how many times each word occurs, listed in the order the words first appear in the speech.
 Read one line of text and, for each distinct word in the order of its first appearance, print `word:count` on its own line, where count is how many times that word occurs.
-### Input Format
-- Line 1: A sentence (words separated by spaces)
-### Output Format
-```
-a:3
-b:2
-c:1
-```
 ### Example Walkthrough
 In the sample sentence `a b a c b a`, the word `a` occurs 3 times, `b` occurs 2 times and `c` occurs once. Listing them in order of first appearance gives the three lines `a:3`, `b:2` and `c:1`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1595,9 +1549,9 @@
           <t>words = input().split()
 counts = {}
 for w in words:
-    counts[w] = counts.get(w, 0) + 1
+    counts[w] = counts.get(w, 0) + 1   # start at 0 the first time a word appears
 for w, c in counts.items():
-    print(f"{w}:{c}")</t>
+    print(f"{w}:{c}")   # dicts remember insertion order, so first-seen order is kept</t>
         </is>
       </c>
     </row>
@@ -1611,19 +1565,11 @@
         <is>
           <t>A maths teacher is preparing a quick-reference chart of square numbers for the classroom wall. Given a rough list of numbers (possibly with repeats and in any order), the chart must show each number once, in increasing order, next to its square.
 Read a line of space-separated numbers. For each distinct number, taken in ascending order, print a line in the form `number:square`. Build the number-to-square mapping using a dictionary comprehension.
-### Input Format
-- Line 1: Space-separated numbers
-### Output Format
-```
-1:1
-2:4
-3:9
-```
 ### Example Walkthrough
 The sample input `3 1 2` contains the distinct numbers 1, 2 and 3. In ascending order their squares are 1, 4 and 9, so the program prints the lines `1:1`, `2:4` and `3:9`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1769,8 +1715,8 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>nums = sorted(set(map(int, input().split())))
-squares = {x: x * x for x in nums}
+          <t>nums = sorted(set(map(int, input().split())))   # drop duplicates, then sort ascending
+squares = {x: x * x for x in nums}   # dictionary comprehension maps each number to its square
 for x in nums:
     print(f"{x}:{squares[x]}")</t>
         </is>
@@ -1786,18 +1732,11 @@
         <is>
           <t>It is class representative election day. Each student writes one candidate's name on a slip and drops it in a box, and the class teacher counts the slips one by one. The candidate with the most votes wins; if two candidates tie, the name that comes first alphabetically is declared the winner.
 Read `N`, then `N` lines each containing one candidate name (one vote per line). Print the name of the winner — the candidate with the most votes, using alphabetical order to break any tie.
-### Input Format
-- Line 1: `N`, the number of votes
-- Next `N` lines: one candidate name each
-### Output Format
-```
-asha
-```
 ### Example Walkthrough
 The sample box has 5 slips: `asha` gets 3 votes while `kabir` and `meera` get 1 each. With the most votes, `asha` wins, so the program prints `asha`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1961,9 +1900,9 @@
 counts = {}
 for _ in range(n):
     name = input()
-    counts[name] = counts.get(name, 0) + 1
-best = max(counts.values())
-winners = sorted(name for name, c in counts.items() if c == best)
+    counts[name] = counts.get(name, 0) + 1   # tally one vote per name
+best = max(counts.values())   # highest vote count
+winners = sorted(name for name, c in counts.items() if c == best)   # alphabetical tie-break
 print(winners[0])</t>
         </is>
       </c>
@@ -1978,17 +1917,11 @@
         <is>
           <t>A quiz show logs the answer submitted by each contestant during a round, and popular answers are often repeated by many contestants. The host wants to know how many genuinely different answers were given, not how many contestants answered.
 Write a program that reads a line of space-separated words and prints how many distinct words it contains, counting each different word only once.
-### Input Format
-- Line 1: Space-separated words
-### Output Format
-```
-3
-```
 ### Example Walkthrough
 In the sample, the answers are `1 2 2 3`. Even though there are four entries, the different values are only 1, 2, and 3, so the program prints `3`.
 ### Constraints
 - The input line has at least one value.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -2120,7 +2053,7 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>print(len(set(input().split())))</t>
+          <t>print(len(set(input().split())))   # set drops duplicate words, len counts what's left</t>
         </is>
       </c>
     </row>
@@ -2134,18 +2067,11 @@
         <is>
           <t>Two class representatives each submit a guest list of names invited to a joint event, and the organizer needs a single combined guest list with every name that appears on either list, with no repeats, in alphabetical order.
 Write a program that reads two lines of space-separated names and prints every name that appears in at least one of the two lists, sorted alphabetically and separated by single spaces, with no duplicates.
-### Input Format
-- Line 1: Space-separated names (first list)
-- Line 2: Space-separated names (second list)
-### Output Format
-```
-asha meena rohan
-```
 ### Example Walkthrough
 In the sample, the first list is `asha rohan` and the second is `meena asha`. Combining both lists and removing the repeated `asha` gives `asha`, `meena`, and `rohan`, which sorted alphabetically prints as `asha meena rohan`.
 ### Constraints
 - The inputs are valid lines of space-separated names.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -2284,463 +2210,260 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>a=set(input().split()); b=set(input().split()); print(*sorted(a|b))</t>
+          <t>a=set(input().split()); b=set(input().split()); print(*sorted(a|b))   # | unions both sets, sorted() orders the result</t>
         </is>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AH11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>explanation</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>difficulty</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>bloomTaxonomy</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>tags</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>subjects</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>topics</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>subTopics</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>companies</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>codingType</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>language</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>supportAllLanguages</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>enablePartialScore</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>ignoreCase</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>testcase1_input</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>testcase1_output</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>testcase2_input</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>testcase2_output</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>testcase3_input</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>testcase3_output</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>testcase4_input</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>testcase4_output</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>testcase5_input</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>testcase5_output</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>testcase6_input</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>testcase6_output</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>testcase7_input</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>testcase7_output</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>preloadCode_python</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>solution_python</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>hints</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Python - Set Report</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>On sports day, the PE teacher has two sign-up sheets of student numbers — one for cricket and one for kabaddi. For the report she needs three counts: how many students signed up in total, how many signed up for both games, and how many chose only cricket.
 Read two lines of space-separated numbers. Treating each line as a set (repeats don't matter), print three lines: `Union: X` where X counts the values present in either line, `Intersection: Y` where Y counts the values present in both, and `Only first: Z` where Z counts the values in the first line but not the second.
-### Input Format
-- Line 1: First list of numbers
-- Line 2: Second list of numbers
-### Output Format
-```
-Union: 5
-Intersection: 2
-Only first: 2
-```
 ### Example Walkthrough
 The sample sets are `{1, 2, 3, 4}` and `{3, 4, 5}`. Together they contain the 5 values 1-5, the values 3 and 4 are in both, and only 1 and 2 are in the first but not the second — so the program prints `Union: 5`, `Intersection: 2` and `Only first: 2`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
         <v>5</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>sets-and-dictionaries</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>set-operations</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O2" t="b">
+      <c r="O12" t="b">
         <v>0</v>
       </c>
-      <c r="P2" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q2" t="b">
-        <v>1</v>
-      </c>
-      <c r="R2" t="inlineStr">
+      <c r="P12" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="b">
+        <v>1</v>
+      </c>
+      <c r="R12" t="inlineStr">
         <is>
           <t>1 2 3 4
 3 4 5</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>Union: 5
 Intersection: 2
 Only first: 2</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>1 2
 3 4</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Union: 4
 Intersection: 0
 Only first: 2</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>1 2 3
 1 2 3</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Union: 3
 Intersection: 3
 Only first: 0</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>0
 0</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Union: 1
 Intersection: 1
 Only first: 0</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="Z12" t="inlineStr">
         <is>
           <t>1 2 3
 4 5 6</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>Union: 6
 Intersection: 0
 Only first: 3</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>-1 -2
 -2 -3</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>Union: 3
 Intersection: 1
 Only first: 1</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AD12" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6 7 8
 4 5 6 7 8 9 10</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AE12" t="inlineStr">
         <is>
           <t>Union: 10
 Intersection: 5
 Only first: 3</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AG12" t="inlineStr">
         <is>
           <t>a = set(map(int, input().split()))
 b = set(map(int, input().split()))
-print(f"Union: {len(a | b)}")
-print(f"Intersection: {len(a &amp; b)}")
-print(f"Only first: {len(a - b)}")</t>
+print(f"Union: {len(a | b)}")   # | combines both sets
+print(f"Intersection: {len(a &amp; b)}")   # &amp; keeps values in both sets
+print(f"Only first: {len(a - b)}")   # - keeps values only in the first set</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Python - Passing Students</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>The exam cell is preparing the pass list after the internal test. The pass mark is 40: every student scoring 40 or more makes it onto the list, which is pinned up with the names in alphabetical order.
 Read `N`, then `N` lines each containing a student's name and score. Using a dictionary comprehension, keep only the students who scored 40 or more, and print their names in alphabetical order, one per line.
-### Input Format
-- Line 1: `N`, the number of students
-- Next `N` lines: `name score`
-### Output Format
-```
-asha
-meera
-```
 ### Example Walkthrough
 In the sample, `asha` scored 80 and `meera` scored 55 — both 40 or more — while `kabir` scored 30 and misses the list. Sorted alphabetically, the pass list is `asha` then `meera`, one name per line.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
         <v>5</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>sets-and-dictionaries</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>dictionary-comprehensions</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O3" t="b">
+      <c r="O13" t="b">
         <v>0</v>
       </c>
-      <c r="P3" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q3" t="b">
-        <v>1</v>
-      </c>
-      <c r="R3" t="inlineStr">
+      <c r="P13" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="b">
+        <v>1</v>
+      </c>
+      <c r="R13" t="inlineStr">
         <is>
           <t>3
 asha 80
@@ -2748,47 +2471,47 @@
 meera 55</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>asha
 meera</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>1
 sam 40</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>sam</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>2
 a 90
 b 20</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>1
 zed 39</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>4
 a 40
@@ -2797,13 +2520,13 @@
 d 0</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AC13" t="inlineStr">
         <is>
           <t>a
 c</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AD13" t="inlineStr">
         <is>
           <t>5
 p 41
@@ -2813,584 +2536,560 @@
 t 38</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AE13" t="inlineStr">
         <is>
           <t>p
 q
 s</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AG13" t="inlineStr">
         <is>
           <t>n = int(input())
 students = {}
 for _ in range(n):
     name, score = input().split()
-    students[name] = int(score)
-passed = {name: score for name, score in students.items() if score &gt;= 40}
+    students[name] = int(score)   # store score as int so it can be compared
+passed = {name: score for name, score in students.items() if score &gt;= 40}   # keep only passing scores
 for name in sorted(passed):
     print(name)</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Python - Sorted Unique</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Read a line of space-separated numbers and print each distinct value once, sorted from smallest to largest, separated by spaces.
-### Input Format
-- Line 1: Space-separated numbers
-### Output Format
-```
-1 2 3
-```
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>A library is running a book donation drive where donors drop off used book ID numbers into a box, and duplicates come in often since siblings or friends donate the same titles. The librarian wants a clean, sorted list of the distinct book IDs collected so far.
+Read a line of space-separated numbers and print each distinct value once, sorted from smallest to largest, separated by spaces.
 ### Example Walkthrough
-In the sample, the numbers are `3 1 2 1 3`. The distinct values, sorted, are `1`, `2`, and `3`, so the program prints `1 2 3`.
+In the sample, the numbers are `3 1 2 3 1`. The distinct values, sorted, are `1`, `2`, and `3`, so the program prints `1 2 3`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
         <v>5</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>sets-and-dictionaries</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>sets</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O4" t="b">
+      <c r="O14" t="b">
         <v>0</v>
       </c>
-      <c r="P4" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q4" t="b">
-        <v>1</v>
-      </c>
-      <c r="R4" t="inlineStr">
+      <c r="P14" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="b">
+        <v>1</v>
+      </c>
+      <c r="R14" t="inlineStr">
         <is>
           <t>3 1 2 3 1</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>1 2 3</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>4 4 4 2 2</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>2 4</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Y14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>-1 -2 -1 -2</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AA14" t="inlineStr">
         <is>
           <t>-2 -1</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AB14" t="inlineStr">
         <is>
           <t>7 7 7 7</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AC14" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AD14" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6 7 8 9 10</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AE14" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6 7 8 9 10</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr">
+      <c r="AG14" t="inlineStr">
         <is>
           <t>nums = list(map(int, input().split()))
-print(*sorted(set(nums)))</t>
+print(*sorted(set(nums)))   # set drops duplicates, sorted() then orders what's left</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Python - In Either List</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Read two lines of space-separated numbers and print all values that appear in either list, each once, sorted, separated by spaces.
-### Input Format
-- Line 1: First list
-- Line 2: Second list
-### Output Format
-```
-1 2 3
-```
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Two class sections, 10-A and 10-B, are collecting sign-ups for an inter-class quiz competition, and a student's roll number might appear on either section's list. The event coordinator wants a single roll call of everyone who signed up in either section, without listing anyone twice.
+Read two lines of space-separated numbers and print all values that appear in either list, each once, sorted, separated by spaces.
 ### Example Walkthrough
 In the sample, the lists are `1 2` and `2 3`. The values in either list are `1`, `2`, and `3`, so the program prints `1 2 3`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
         <v>5</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>sets-and-dictionaries</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>set-operations</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O5" t="b">
+      <c r="O15" t="b">
         <v>0</v>
       </c>
-      <c r="P5" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" t="b">
-        <v>1</v>
-      </c>
-      <c r="R5" t="inlineStr">
+      <c r="P15" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="b">
+        <v>1</v>
+      </c>
+      <c r="R15" t="inlineStr">
         <is>
           <t>1 2
 2 3</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>1 2 3</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>5
 6</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>5 6</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>1 1
 2 2</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>1 2</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>0
 0</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Y15" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>1 2 3
 4 5 6</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AA15" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AB15" t="inlineStr">
         <is>
           <t>-1 -2
 -2 -3</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AC15" t="inlineStr">
         <is>
           <t>-3 -2 -1</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AD15" t="inlineStr">
         <is>
           <t>1 2 3 4 5
 5 6 7 8 9</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AE15" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6 7 8 9</t>
         </is>
       </c>
-      <c r="AG5" t="inlineStr">
+      <c r="AG15" t="inlineStr">
         <is>
           <t>a = set(map(int, input().split()))
 b = set(map(int, input().split()))
-print(*sorted(a | b))</t>
+print(*sorted(a | b))   # | combines both sets, removing duplicates</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Python - Only in the First</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Read two lines of space-separated numbers and print the values that are in the first list but not the second, sorted, separated by spaces.
-### Input Format
-- Line 1: First list
-- Line 2: Second list
-### Output Format
-```
-1 3
-```
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>A sports committee is organizing cricket trials and badminton trials, and some students registered for both. The coach wants to know which students registered only for the cricket trials and skipped badminton, so extra practice slots can be offered to them.
+Read two lines of space-separated numbers and print the values that are in the first list but not the second, sorted, separated by spaces.
 ### Example Walkthrough
-In the sample, the lists are `1 2 3` and `2`. Removing `2` from the first list leaves `1` and `3`, so the program prints `1 3`.
+In the sample, the lists are `1 2 3` and `2 4`. Removing anything that also appears in the second list (`2`) leaves `1` and `3`, so the program prints `1 3`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
         <v>5</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>sets-and-dictionaries</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>set-operations</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O6" t="b">
+      <c r="O16" t="b">
         <v>0</v>
       </c>
-      <c r="P6" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q6" t="b">
-        <v>1</v>
-      </c>
-      <c r="R6" t="inlineStr">
+      <c r="P16" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="b">
+        <v>1</v>
+      </c>
+      <c r="R16" t="inlineStr">
         <is>
           <t>1 2 3
 2 4</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>1 3</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>5 6 7
 6</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>5 7</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>1 2 3
 4 5 6</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>1 2 3</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>0
 0</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>1 2 3
 1 2 3</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AB16" t="inlineStr">
         <is>
           <t>-1 -2 -3
 -2</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AC16" t="inlineStr">
         <is>
           <t>-3 -1</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AD16" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6 7 8
 2 4 6 8</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AE16" t="inlineStr">
         <is>
           <t>1 3 5 7</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr">
+      <c r="AG16" t="inlineStr">
         <is>
           <t>a = set(map(int, input().split()))
 b = set(map(int, input().split()))
-print(*sorted(a - b))</t>
+print(*sorted(a - b))   # - keeps values in the first set but not the second</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Python - Key Exists</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Read `N` key/value entries, then a key. Print 'Yes' if that key is present, otherwise print 'No'.
-### Input Format
-- Line 1: N
-- Next N lines: 'key value'
-- Last line: key to check
-### Output Format
-```
-Yes
-```
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>A hostel warden keeps a register of room allocations as key/value entries, one per resident, and occasionally needs to quickly check whether a particular resident's name is already recorded before adding them again.
+Read `N` key/value entries, then a key. Print 'Yes' if that key is present, otherwise print 'No'.
 ### Example Walkthrough
-In the sample, `N` is `2` with entries `a 1` and `b 2`, and the key to check is `a`. Since `a` is present, the program prints `Yes`.
+In the sample, `N` is `2` with entries `apple 3` and `banana 5`, and the key to check is `apple`. Since `apple` is present, the program prints `Yes`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
         <v>5</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>sets-and-dictionaries</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>dictionary-operations</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O7" t="b">
+      <c r="O17" t="b">
         <v>0</v>
       </c>
-      <c r="P7" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q7" t="b">
-        <v>1</v>
-      </c>
-      <c r="R7" t="inlineStr">
+      <c r="P17" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q17" t="b">
+        <v>1</v>
+      </c>
+      <c r="R17" t="inlineStr">
         <is>
           <t>2
 apple 3
@@ -3398,24 +3097,24 @@
 apple</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>1
 x 1
 y</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>2
 a 1
@@ -3423,35 +3122,35 @@
 b</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>0
 z</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Y17" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>1
 solo 9
 solo</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AA17" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AB17" t="inlineStr">
         <is>
           <t>3
 a 1
@@ -3460,12 +3159,12 @@
 d</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AC17" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AD17" t="inlineStr">
         <is>
           <t>4
 p 1
@@ -3475,12 +3174,12 @@
 r</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AE17" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
+      <c r="AG17" t="inlineStr">
         <is>
           <t>n = int(input())
 data = {}
@@ -3488,414 +3187,395 @@
     key, value = input().split()
     data[key] = value
 query = input()
-print("Yes" if query in data else "No")</t>
+print("Yes" if query in data else "No")   # 'in' checks dictionary keys, not values</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Python - Unique Words</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Read a sentence and print how many distinct words it contains.
-### Input Format
-- Line 1: A sentence
-### Output Format
-```
-3
-```
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>A college is running an essay-writing contest, and one of the judging criteria is vocabulary richness. Given a submitted sentence, the judges want to know how many distinct words the student actually used.
+Read a sentence and print how many distinct words it contains.
 ### Example Walkthrough
-In the sample, the sentence is `a b a c`. The distinct words are `a`, `b`, and `c` - three in total - so the program prints `3`.
+In the sample, the sentence is `the cat the dog`. The distinct words are `the`, `cat`, and `dog` - three in total - so the program prints `3`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
         <v>5</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>sets-and-dictionaries</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>sets</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O8" t="b">
+      <c r="O18" t="b">
         <v>0</v>
       </c>
-      <c r="P8" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q8" t="b">
-        <v>1</v>
-      </c>
-      <c r="R8" t="inlineStr">
+      <c r="P18" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q18" t="b">
+        <v>1</v>
+      </c>
+      <c r="R18" t="inlineStr">
         <is>
           <t>the cat the dog</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>hello</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>a a a a</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Y18" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>one two three four five</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AA18" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AB18" t="inlineStr">
         <is>
           <t>cat cat dog dog bird</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AC18" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AD18" t="inlineStr">
         <is>
           <t>a b a b a b a b</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AE18" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
+      <c r="AG18" t="inlineStr">
         <is>
           <t>words = input().split()
-print(len(set(words)))</t>
+print(len(set(words)))   # set drops duplicate words, len counts what's left</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Python - Set Membership</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Read a line of space-separated values, then a value. Print 'Yes' if the value is in the set of values, otherwise print 'No'.
-### Input Format
-- Line 1: Space-separated values
-- Line 2: The value to check
-### Output Format
-```
-Yes
-```
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>At a college cultural fest, volunteers are given a list of registered participant IDs to check against as attendees arrive at the gate, and a coordinator wants to quickly confirm whether a given ID is on the list.
+Read a line of space-separated values, then a value. Print 'Yes' if the value is in the set of values, otherwise print 'No'.
 ### Example Walkthrough
-In the sample, the values are `a b c` and the value to check is `b`. Since `b` is among the values, the program prints `Yes`.
+In the sample, the values are `1 2 3 4` and the value to check is `3`. Since `3` is among the values, the program prints `Yes`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
         <v>5</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>sets-and-dictionaries</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>sets</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O9" t="b">
+      <c r="O19" t="b">
         <v>0</v>
       </c>
-      <c r="P9" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q9" t="b">
-        <v>1</v>
-      </c>
-      <c r="R9" t="inlineStr">
+      <c r="P19" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q19" t="b">
+        <v>1</v>
+      </c>
+      <c r="R19" t="inlineStr">
         <is>
           <t>1 2 3 4
 3</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>a b c
 z</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>5 5 5
 5</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>a
 a</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Y19" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="Z19" t="inlineStr">
         <is>
           <t>1 2 3
 9</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AA19" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AB19" t="inlineStr">
         <is>
           <t>x x x x
 x</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AC19" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AD19" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6 7 8 9 10
 10</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AE19" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AG9" t="inlineStr">
+      <c r="AG19" t="inlineStr">
         <is>
           <t>values = set(input().split())
 query = input()
-print("Yes" if query in values else "No")</t>
+print("Yes" if query in values else "No")   # sets give fast membership checks</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Python - Dictionary Lookup</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>A hostel's key-card office keeps a lookup table mapping each resident's name to their card ID. When a resident's name is queried at the front desk, the system needs to report the matching card ID, or say the name isn't registered.
 Write a program that reads a whole number N, then reads N lines each with a name and an ID separated by a space and stores them in a dictionary, then reads one more name and prints its ID if it exists in the dictionary, or `Not found` otherwise.
-### Input Format
-- Line 1: N, the number of registered residents
-- Next N lines: name and ID separated by a space
-- Final line: the name being queried
-### Output Format
-```
-111
-```
 ### Example Walkthrough
 In the sample, N is 2 with `Asha 111` and `Rohan 222` registered, and the query is `Asha`. Since Asha is in the dictionary with ID `111`, the program prints `111`.
 ### Constraints
 - Names and IDs are valid strings with no spaces within them.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
         <v>5</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>sets-and-dictionaries</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>dictionaries</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O10" t="b">
+      <c r="O20" t="b">
         <v>0</v>
       </c>
-      <c r="P10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" t="b">
-        <v>1</v>
-      </c>
-      <c r="R10" t="inlineStr">
+      <c r="P20" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q20" t="b">
+        <v>1</v>
+      </c>
+      <c r="R20" t="inlineStr">
         <is>
           <t>2
 Asha 111
@@ -3903,35 +3583,35 @@
 Asha</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>111</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>1
 Meena 333
 Rohan</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>0
 X</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>3
 A 1
@@ -3940,24 +3620,24 @@
 C</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Y20" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="Z20" t="inlineStr">
         <is>
           <t>1
 Z 9
 Z</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AA20" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AB20" t="inlineStr">
         <is>
           <t>2
 Dev 10
@@ -3965,12 +3645,12 @@
 Dev</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AC20" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AD20" t="inlineStr">
         <is>
           <t>2
 A 1
@@ -3978,135 +3658,128 @@
 D</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AE20" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>n=int(input()); d={}
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>n=int(input()); d={}   # d will map each key to its value
 for _ in range(n):
  k,v=input().split(); d[k]=v
-print(d.get(input(),"Not found"))</t>
+print(d.get(input(),"Not found"))   # get() returns a default when the key is missing</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Python - Value Total</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>A canteen till reads a list of item names and prices punched in one per line during the day and needs the total bill amount collected across all of them.
 Write a program that reads a whole number N, then reads N lines each with an item name and a price separated by a space, and prints the sum of all the prices.
-### Input Format
-- Line 1: N, the number of items
-- Next N lines: item name and price separated by a space
-### Output Format
-```
-5
-```
 ### Example Walkthrough
 In the sample, N is 2 with `pen 3` and `book 2`. Adding the prices 3 and 2 gives 5, so the program prints `5`.
 ### Constraints
 - Item names contain no spaces, and prices are valid whole numbers.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
         <v>5</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>sets-and-dictionaries</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>dictionary-operations</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O11" t="b">
+      <c r="O21" t="b">
         <v>0</v>
       </c>
-      <c r="P11" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q11" t="b">
-        <v>1</v>
-      </c>
-      <c r="R11" t="inlineStr">
+      <c r="P21" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q21" t="b">
+        <v>1</v>
+      </c>
+      <c r="R21" t="inlineStr">
         <is>
           <t>2
 pen 3
 book 2</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>1
 a 10</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>3
 x 1
@@ -4114,24 +3787,24 @@
 z 3</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Y21" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="Z21" t="inlineStr">
         <is>
           <t>2
 a -1
 b 5</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AA21" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AB21" t="inlineStr">
         <is>
           <t>4
 p 1
@@ -4140,532 +3813,336 @@
 s 1</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AC21" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AD21" t="inlineStr">
         <is>
           <t>1
 only 0</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AE21" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>n=int(input()); total=0
-for _ in range(n): total+=int(input().split()[1])
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>n=int(input()); total=0   # start a running total at 0
+for _ in range(n): total+=int(input().split()[1])   # add just the second value from each line
 print(total)</t>
         </is>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AH11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>explanation</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>difficulty</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>bloomTaxonomy</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>tags</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>subjects</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>topics</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>subTopics</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>companies</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>codingType</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>language</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>supportAllLanguages</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>enablePartialScore</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>ignoreCase</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>testcase1_input</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>testcase1_output</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>testcase2_input</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>testcase2_output</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>testcase3_input</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>testcase3_output</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>testcase4_input</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>testcase4_output</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>testcase5_input</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>testcase5_output</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>testcase6_input</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>testcase6_output</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>testcase7_input</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>testcase7_output</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>preloadCode_python</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>solution_python</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>hints</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Python - Most Common Word</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Read a sentence and print the word that appears most often. If several tie, print the one that appears first.
-### Input Format
-- Line 1: A sentence
-### Output Format
-```
-a
-```
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>A professor collects one-line feedback comments after a workshop and wants a quick sense of what students talk about most, by finding the word that appears most often in a given comment.
+Read a sentence and print the word that appears most often. If several tie, print the one that appears first.
 ### Example Walkthrough
-In the sample, the sentence is `a b a c a b`. The word `a` appears `3` times, more than any other word, so the program prints `a`.
+In the sample, the sentence is `a b a c a`. The word `a` appears `3` times, more than any other word, so the program prints `a`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
         <v>5</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>sets-and-dictionaries</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>dictionary-operations</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O2" t="b">
+      <c r="O22" t="b">
         <v>0</v>
       </c>
-      <c r="P2" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q2" t="b">
-        <v>1</v>
-      </c>
-      <c r="R2" t="inlineStr">
+      <c r="P22" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q22" t="b">
+        <v>1</v>
+      </c>
+      <c r="R22" t="inlineStr">
         <is>
           <t>a b a c a</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>dog cat dog cat</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t>dog</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="V22" t="inlineStr">
         <is>
           <t>one</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>one</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>solo</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Y22" t="inlineStr">
         <is>
           <t>solo</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="Z22" t="inlineStr">
         <is>
           <t>x x y y y</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AA22" t="inlineStr">
         <is>
           <t>y</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AB22" t="inlineStr">
         <is>
           <t>a b c a b c a</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AC22" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AD22" t="inlineStr">
         <is>
           <t>cat dog cat dog bird</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AE22" t="inlineStr">
         <is>
           <t>cat</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AG22" t="inlineStr">
         <is>
           <t>words = input().split()
 counts = {}
 for w in words:
-    counts[w] = counts.get(w, 0) + 1
-best = max(counts.values())
+    counts[w] = counts.get(w, 0) + 1   # tally occurrences of each word
+best = max(counts.values())   # highest count seen
 for w in words:
     if counts[w] == best:
-        print(w)
+        print(w)   # first word, in original order, that reaches the highest count
         break</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>Python - Evens and Odds</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Read a line of space-separated numbers and print how many are even and how many are odd in the form 'even X odd Y'.
-### Input Format
-- Line 1: Space-separated numbers
-### Output Format
-```
-even 2 odd 3
-```
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>A lab instructor is splitting a class into two batches for a practical exam based on roll numbers, sending even roll numbers to one batch and odd roll numbers to the other, and wants a quick count of how many students land in each batch.
+Read a line of space-separated numbers and print how many are even and how many are odd in the form 'even X odd Y'.
 ### Example Walkthrough
 In the sample, the numbers are `1 2 3 4 5`. There are `2` even numbers (`2`, `4`) and `3` odd numbers (`1`, `3`, `5`), so the program prints `even 2 odd 3`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
         <v>5</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>sets-and-dictionaries</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>dictionary-operations</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O3" t="b">
+      <c r="O23" t="b">
         <v>0</v>
       </c>
-      <c r="P3" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q3" t="b">
-        <v>1</v>
-      </c>
-      <c r="R3" t="inlineStr">
+      <c r="P23" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q23" t="b">
+        <v>1</v>
+      </c>
+      <c r="R23" t="inlineStr">
         <is>
           <t>1 2 3 4 5</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>even 2 odd 3</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>2 4 6</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>even 3 odd 0</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="V23" t="inlineStr">
         <is>
           <t>1 3 5</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="W23" t="inlineStr">
         <is>
           <t>even 0 odd 3</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Y23" t="inlineStr">
         <is>
           <t>even 1 odd 0</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="Z23" t="inlineStr">
         <is>
           <t>-2 -4 -1 -3</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AA23" t="inlineStr">
         <is>
           <t>even 2 odd 2</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AB23" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AC23" t="inlineStr">
         <is>
           <t>even 0 odd 1</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AD23" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6 7 8 9 10</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AE23" t="inlineStr">
         <is>
           <t>even 5 odd 5</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AG23" t="inlineStr">
         <is>
           <t>nums = list(map(int, input().split()))
-counts = {"even": 0, "odd": 0}
+counts = {"even": 0, "odd": 0}   # dictionary tracks two running totals
 for x in nums:
     if x % 2 == 0:
         counts["even"] += 1
@@ -4675,404 +4152,385 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>Python - Repeated Values</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Read a line of space-separated numbers and print the values that appear more than once, sorted, separated by spaces.
-### Input Format
-- Line 1: Space-separated numbers
-### Output Format
-```
-2 3
-```
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>A college fest is running a lucky draw, and ticket numbers are typed in by hand at the counter, which sometimes causes the same ticket number to be entered more than once by mistake. The organizers want to flag which ticket numbers were entered more than once so they can be corrected before the draw.
+Read a line of space-separated numbers and print the values that appear more than once, sorted, separated by spaces.
 ### Example Walkthrough
-In the sample, the numbers are `1 2 2 3 3`. The values `2` and `3` each appear more than once, so the program prints `2 3`.
+In the sample, the numbers are `1 2 2 3 3 4`. The values `2` and `3` each appear more than once, so the program prints `2 3`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
         <v>5</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>sets-and-dictionaries</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>dictionary-operations</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O4" t="b">
+      <c r="O24" t="b">
         <v>0</v>
       </c>
-      <c r="P4" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q4" t="b">
-        <v>1</v>
-      </c>
-      <c r="R4" t="inlineStr">
+      <c r="P24" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q24" t="b">
+        <v>1</v>
+      </c>
+      <c r="R24" t="inlineStr">
         <is>
           <t>1 2 2 3 3 4</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>2 3</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>5 5 6 6</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="U24" t="inlineStr">
         <is>
           <t>5 6</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="V24" t="inlineStr">
         <is>
           <t>1 1 2 2 3</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="W24" t="inlineStr">
         <is>
           <t>1 2</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="Z24" t="inlineStr">
         <is>
           <t>1 2 3 4 5</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AB24" t="inlineStr">
         <is>
           <t>7 7 7 7 7</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AC24" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AD24" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6 7 8 9 10 1 2 3</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AE24" t="inlineStr">
         <is>
           <t>1 2 3</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr">
+      <c r="AG24" t="inlineStr">
         <is>
           <t>nums = list(map(int, input().split()))
 counts = {}
 for x in nums:
-    counts[x] = counts.get(x, 0) + 1
-repeated = sorted(v for v, c in counts.items() if c &gt; 1)
+    counts[x] = counts.get(x, 0) + 1   # count how many times each value appears
+repeated = sorted(v for v, c in counts.items() if c &gt; 1)   # keep only values seen more than once
 print(*repeated)</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Python - First Unique Character</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Read a word and print the first character that appears exactly once. If every character repeats, print 'None'.
-### Input Format
-- Line 1: A word
-### Output Format
-```
-c
-```
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>A cryptography club is designing a simple typing puzzle where players must spot the first character in a scrambled word that doesn't repeat anywhere else in it, as a warm-up before harder cipher challenges.
+Read a word and print the first character that appears exactly once. If every character repeats, print 'None'.
 ### Example Walkthrough
 In the sample, the word is `aabbc`. Both `a` and `b` repeat, but `c` appears only once and is the first such character, so the program prints `c`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
         <v>5</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>sets-and-dictionaries</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>dictionary-operations</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O5" t="b">
+      <c r="O25" t="b">
         <v>0</v>
       </c>
-      <c r="P5" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" t="b">
-        <v>1</v>
-      </c>
-      <c r="R5" t="inlineStr">
+      <c r="P25" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q25" t="b">
+        <v>1</v>
+      </c>
+      <c r="R25" t="inlineStr">
         <is>
           <t>aabbc</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>aabb</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="V25" t="inlineStr">
         <is>
           <t>xyz</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="W25" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Y25" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="Z25" t="inlineStr">
         <is>
           <t>aabbccd</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AA25" t="inlineStr">
         <is>
           <t>d</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AB25" t="inlineStr">
         <is>
           <t>zzzzz</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AC25" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AD25" t="inlineStr">
         <is>
           <t>abababc</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AE25" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="AG5" t="inlineStr">
+      <c r="AG25" t="inlineStr">
         <is>
           <t>word = input()
 counts = {}
 for ch in word:
-    counts[ch] = counts.get(ch, 0) + 1
+    counts[ch] = counts.get(ch, 0) + 1   # count occurrences of each character
 answer = "None"
 for ch in word:
     if counts[ch] == 1:
-        answer = ch
+        answer = ch   # first character, in order, that appears exactly once
         break
 print(answer)</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>Python - Merge Dictionaries</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Read a first set of `N` key/value pairs, then a second set of `M` key/value pairs. Merge them so that keys in the second set overwrite the first, and print every 'key:value' with keys sorted.
-### Input Format
-- Line 1: N
-- Next N lines: 'key value'
-- Then: M
-- Next M lines: 'key value'
-### Output Format
-```
-a:1
-b:9
-```
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>The hostel mess committee has a default weekly menu stored as item-to-price pairs, and today the cook has announced a few special-item price changes that should override the defaults wherever they overlap.
+Read a first set of `N` key/value pairs, then a second set of `M` key/value pairs. Merge them so that keys in the second set overwrite the first, and print every 'key:value' with keys sorted.
 ### Example Walkthrough
 In the sample, the first set has `a 1` and `b 2`, and the second set has `b 9`. Merging them lets the second set's `b` overwrite the first, so the program prints `a:1` then `b:9`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
         <v>5</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>sets-and-dictionaries</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>dictionary-operations</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O6" t="b">
+      <c r="O26" t="b">
         <v>0</v>
       </c>
-      <c r="P6" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q6" t="b">
-        <v>1</v>
-      </c>
-      <c r="R6" t="inlineStr">
+      <c r="P26" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q26" t="b">
+        <v>1</v>
+      </c>
+      <c r="R26" t="inlineStr">
         <is>
           <t>2
 a 1
@@ -5081,13 +4539,13 @@
 b 9</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>a:1
 b:9</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t>1
 x 5
@@ -5095,13 +4553,13 @@
 y 6</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t>x:5
 y:6</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="V26" t="inlineStr">
         <is>
           <t>2
 p 1
@@ -5111,31 +4569,31 @@
 q 4</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="W26" t="inlineStr">
         <is>
           <t>p:3
 q:4</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>0
 0</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="Z26" t="inlineStr">
         <is>
           <t>1
 a 1
 0</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AA26" t="inlineStr">
         <is>
           <t>a:1</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AB26" t="inlineStr">
         <is>
           <t>0
 2
@@ -5143,13 +4601,13 @@
 y 2</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AC26" t="inlineStr">
         <is>
           <t>x:1
 y:2</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AD26" t="inlineStr">
         <is>
           <t>3
 a 1
@@ -5161,7 +4619,7 @@
 e 7</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AE26" t="inlineStr">
         <is>
           <t>a:1
 b:2
@@ -5170,7 +4628,7 @@
 e:7</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr">
+      <c r="AG26" t="inlineStr">
         <is>
           <t>merged = {}
 n = int(input())
@@ -5180,94 +4638,87 @@
 m = int(input())
 for _ in range(m):
     key, value = input().split()
-    merged[key] = value
+    merged[key] = value   # later entries overwrite earlier ones with the same key
 for key in sorted(merged):
     print(f"{key}:{merged[key]}")</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>Python - Spending by Category</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Read `N` spending records, each a category and an amount. Print each category's total as 'category:total', with categories sorted alphabetically.
-### Input Format
-- Line 1: N
-- Next N lines: 'category amount'
-### Output Format
-```
-food:130
-travel:50
-```
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>A hostel student tracks daily expenses in a simple notebook app, logging each purchase with a category and an amount, and at the end of the week wants to see the total spent in each category.
+Read `N` spending records, each a category and an amount. Print each category's total as 'category:total', with categories sorted alphabetically.
 ### Example Walkthrough
 In the sample, `N` is `3` with records `food 100`, `travel 50`, and `food 30`. The `food` entries total `130` and `travel` totals `50`, so the program prints `food:130` then `travel:50`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
         <v>5</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>sets-and-dictionaries</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>dictionary-operations</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O7" t="b">
+      <c r="O27" t="b">
         <v>0</v>
       </c>
-      <c r="P7" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q7" t="b">
-        <v>1</v>
-      </c>
-      <c r="R7" t="inlineStr">
+      <c r="P27" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q27" t="b">
+        <v>1</v>
+      </c>
+      <c r="R27" t="inlineStr">
         <is>
           <t>3
 food 100
@@ -5275,52 +4726,52 @@
 food 30</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>food:130
 travel:50</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="T27" t="inlineStr">
         <is>
           <t>1
 rent 500</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="U27" t="inlineStr">
         <is>
           <t>rent:500</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="V27" t="inlineStr">
         <is>
           <t>2
 a 5
 a 5</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="W27" t="inlineStr">
         <is>
           <t>a:10</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="Z27" t="inlineStr">
         <is>
           <t>1
 z 0</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AA27" t="inlineStr">
         <is>
           <t>z:0</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AB27" t="inlineStr">
         <is>
           <t>4
 food 10
@@ -5329,14 +4780,14 @@
 bills 40</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AC27" t="inlineStr">
         <is>
           <t>bills:40
 food:40
 travel:20</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AD27" t="inlineStr">
         <is>
           <t>5
 a 1
@@ -5346,131 +4797,124 @@
 c 5</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AE27" t="inlineStr">
         <is>
           <t>a:4
 b:6
 c:5</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
+      <c r="AG27" t="inlineStr">
         <is>
           <t>n = int(input())
 totals = {}
 for _ in range(n):
     category, amount = input().split()
-    totals[category] = totals.get(category, 0) + int(amount)
+    totals[category] = totals.get(category, 0) + int(amount)   # add to the running total per category
 for category in sorted(totals):
     print(f"{category}:{totals[category]}")</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Python - Student Totals</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Read `N` students, each on a line with a name followed by their marks. Print each student's name and total marks as 'name total', with names sorted alphabetically.
-### Input Format
-- Line 1: N
-- Next N lines: 'name mark1 mark2 ...'
-### Output Format
-```
-asha 270
-kabir 180
-```
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>A class teacher enters each student's marks across three subject tests into a spreadsheet-style tool, and needs the total marks computed for every student before ranking the class.
+Read `N` students, each on a line with a name followed by their marks. Print each student's name and total marks as 'name total', with names sorted alphabetically.
 ### Example Walkthrough
-In the sample, `N` is `2` with `asha 90 90 90` and `kabir 60 60 60`. Their totals are `270` and `180`, so the program prints `asha 270` then `kabir 180`.
+In the sample, `N` is `2` with `asha 80 90 100` and `kabir 70 60 50`. Their totals are `270` and `180`, so the program prints `asha 270` then `kabir 180`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
         <v>5</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>sets-and-dictionaries</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>dictionary-operations</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O8" t="b">
+      <c r="O28" t="b">
         <v>0</v>
       </c>
-      <c r="P8" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q8" t="b">
-        <v>1</v>
-      </c>
-      <c r="R8" t="inlineStr">
+      <c r="P28" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q28" t="b">
+        <v>1</v>
+      </c>
+      <c r="R28" t="inlineStr">
         <is>
           <t>2
 asha 80 90 100
 kabir 70 60 50</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>asha 270
 kabir 180</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="T28" t="inlineStr">
         <is>
           <t>1
 sam 40 60</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="U28" t="inlineStr">
         <is>
           <t>sam 100</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="V28" t="inlineStr">
         <is>
           <t>3
 c 1 2
@@ -5478,30 +4922,30 @@
 a 5 6</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="W28" t="inlineStr">
         <is>
           <t>a 11
 b 7
 c 3</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="Z28" t="inlineStr">
         <is>
           <t>1
 solo 0 0 0</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AA28" t="inlineStr">
         <is>
           <t>solo 0</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AB28" t="inlineStr">
         <is>
           <t>4
 zed 10
@@ -5510,7 +4954,7 @@
 beta 40</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AC28" t="inlineStr">
         <is>
           <t>alpha 20
 beta 40
@@ -5518,7 +4962,7 @@
 zed 10</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AD28" t="inlineStr">
         <is>
           <t>5
 p 1 1
@@ -5528,7 +4972,7 @@
 t 5 5</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AE28" t="inlineStr">
         <is>
           <t>p 2
 q 4
@@ -5537,271 +4981,257 @@
 t 10</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
+      <c r="AG28" t="inlineStr">
         <is>
           <t>n = int(input())
 totals = {}
 for _ in range(n):
     parts = input().split()
     name = parts[0]
-    totals[name] = sum(int(m) for m in parts[1:])
+    totals[name] = sum(int(m) for m in parts[1:])   # sum all marks after the name
 for name in sorted(totals):
     print(name, totals[name])</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>Python - Common Names</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>Two hostel wardens each keep a guest list for the weekend, and the security desk needs to know which names appear on both lists, since those visitors need double clearance.
 Write a program that reads two lines of space-separated names and prints only the names that appear in both lists, sorted alphabetically and separated by single spaces. If no name appears on both lists, print an empty line.
-### Input Format
-- Line 1: Space-separated names (first warden's list)
-- Line 2: Space-separated names (second warden's list)
-### Output Format
-```
-b c
-```
 ### Example Walkthrough
 In the sample, the first list is `a b c` and the second is `b c d`. The names appearing on both lists are `b` and `c`, so the program prints `b c`.
 ### Constraints
 - The inputs are valid lines of space-separated names.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
         <v>5</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>sets-and-dictionaries</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>set-operations</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O9" t="b">
+      <c r="O29" t="b">
         <v>0</v>
       </c>
-      <c r="P9" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q9" t="b">
-        <v>1</v>
-      </c>
-      <c r="R9" t="inlineStr">
+      <c r="P29" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q29" t="b">
+        <v>1</v>
+      </c>
+      <c r="R29" t="inlineStr">
         <is>
           <t>a b c
 b c d</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>b c</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="T29" t="inlineStr">
         <is>
           <t>x y
 z</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="V29" t="inlineStr">
         <is>
           <t>same
 same</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="W29" t="inlineStr">
         <is>
           <t>same</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>1 2
 2 3</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Y29" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="Z29" t="inlineStr">
         <is>
           <t>red blue
 blue green</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AA29" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AB29" t="inlineStr">
         <is>
           <t>p
 a</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AD29" t="inlineStr">
         <is>
           <t>m n
 n m</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AE29" t="inlineStr">
         <is>
           <t>m n</t>
         </is>
       </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>a=set(input().split()); b=set(input().split()); print(*sorted(a&amp;b))</t>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>a=set(input().split()); b=set(input().split()); print(*sorted(a&amp;b))   # &amp; keeps names in both sets, then sorts them</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>Python - Character Frequency</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>A typing-speed app analyzes a practice sentence a student typed and reports how many times each character was used (ignoring spaces), sorted alphabetically, to spot which keys need the most practice.
 Write a program that reads a line of text and, for every distinct character other than a space, prints that character and how many times it appears, one per line in the form `&lt;character&gt; &lt;count&gt;`, sorted alphabetically by character.
-### Input Format
-- Line 1: A line of text
-### Output Format
-```
-a 2
-b 1
-```
 ### Example Walkthrough
 In the sample, the text is `aba`. The character `a` appears 2 times and `b` appears 1 time, so the program prints `a 2` then `b 1` in alphabetical order.
 ### Constraints
 - The input is a valid line of text.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
         <v>5</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>sets-and-dictionaries</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>dictionary-operations</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O10" t="b">
+      <c r="O30" t="b">
         <v>0</v>
       </c>
-      <c r="P10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" t="b">
-        <v>1</v>
-      </c>
-      <c r="R10" t="inlineStr">
+      <c r="P30" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q30" t="b">
+        <v>1</v>
+      </c>
+      <c r="R30" t="inlineStr">
         <is>
           <t>aba</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>a 2
 b 1</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="T30" t="inlineStr">
         <is>
           <t>hello</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U30" t="inlineStr">
         <is>
           <t>e 1
 h 1
@@ -5809,43 +5239,43 @@
 o 1</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="V30" t="inlineStr">
         <is>
           <t>a a</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="W30" t="inlineStr">
         <is>
           <t>a 2</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Y30" t="inlineStr">
         <is>
           <t>x 1</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="Z30" t="inlineStr">
         <is>
           <t>1122</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AA30" t="inlineStr">
         <is>
           <t>1 2
 2 2</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AB30" t="inlineStr">
         <is>
           <t>Byte</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AC30" t="inlineStr">
         <is>
           <t>B 1
 e 1
@@ -5853,12 +5283,12 @@
 y 1</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AD30" t="inlineStr">
         <is>
           <t>mississippi</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AE30" t="inlineStr">
         <is>
           <t>i 4
 m 1
@@ -5866,613 +5296,406 @@
 s 4</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>freq={}
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>freq={}   # will hold each character's count
 for ch in input():
- if ch!=" ": freq[ch]=freq.get(ch,0)+1
-for ch in sorted(freq): print(ch, freq[ch])</t>
+ if ch!=" ": freq[ch]=freq.get(ch,0)+1   # skip spaces, count every other character
+for ch in sorted(freq): print(ch, freq[ch])   # print characters in sorted order with their counts</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>Python - Squares Dictionary</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>A number-pattern app for young learners builds a table mapping every number from 1 to N to its square, then shows the squares in order to help students spot the pattern.
 Write a program that reads a whole number N, builds a dictionary mapping each number from 1 to N to its square, and prints just the square values in order, separated by single spaces. If N is 0, print an empty line.
-### Input Format
-- Line 1: N
-### Output Format
-```
-1 4 9
-```
 ### Example Walkthrough
 In the sample, N is 3. The dictionary maps 1 to 1, 2 to 4, and 3 to 9, and printing the values in order gives `1 4 9`.
 ### Constraints
 - All numeric inputs are valid whole numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
         <v>5</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>sets-and-dictionaries</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>dictionary-comprehensions</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O11" t="b">
+      <c r="O31" t="b">
         <v>0</v>
       </c>
-      <c r="P11" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q11" t="b">
-        <v>1</v>
-      </c>
-      <c r="R11" t="inlineStr">
+      <c r="P31" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q31" t="b">
+        <v>1</v>
+      </c>
+      <c r="R31" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="S31" t="inlineStr">
         <is>
           <t>1 4 9</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T31" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U31" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Y31" t="inlineStr">
         <is>
           <t>1 4 9 16 25</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="Z31" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AA31" t="inlineStr">
         <is>
           <t>1 4 9 16 25 36 49</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AB31" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AC31" t="inlineStr">
         <is>
           <t>1 4</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AD31" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AE31" t="inlineStr">
         <is>
           <t>1 4 9 16 25 36 49 64 81 100</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>n=int(input()); d={i:i*i for i in range(1,n+1)}; print(*d.values())</t>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>n=int(input()); d={i:i*i for i in range(1,n+1)}; print(*d.values())   # comprehension maps each number 1..n to its square</t>
         </is>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AH11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>explanation</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>difficulty</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>bloomTaxonomy</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>tags</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>subjects</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>topics</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>subTopics</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>companies</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>codingType</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>language</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>supportAllLanguages</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>enablePartialScore</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>ignoreCase</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>testcase1_input</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>testcase1_output</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>testcase2_input</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>testcase2_output</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>testcase3_input</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>testcase3_output</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>testcase4_input</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>testcase4_output</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>testcase5_input</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>testcase5_output</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>testcase6_input</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>testcase6_output</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>testcase7_input</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>testcase7_output</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>preloadCode_python</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>solution_python</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>hints</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>Python - Word Count Ranking</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Read a sentence and print each distinct word with its count as 'word count', ordered by count from highest to lowest. Break ties alphabetically.
-### Input Format
-- Line 1: A sentence
-### Output Format
-```
-a 3
-b 2
-c 1
-```
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>A teaching assistant scans through a batch of doubt messages posted in the class WhatsApp group and wants a quick ranked summary of which words come up most often, to spot the topics students are struggling with.
+Read a sentence and print each distinct word with its count as 'word count', ordered by count from highest to lowest. Break ties alphabetically.
 ### Example Walkthrough
-In the sample, the sentence is `a b a c a b`. The word `a` appears `3` times, `b` appears `2` times, and `c` appears `1` time, so the program prints `a 3`, `b 2`, and `c 1` in that order.
+In the sample, the sentence is `a b a c b a`. The word `a` appears `3` times, `b` appears `2` times, and `c` appears `1` time, so the program prints `a 3`, `b 2`, and `c 1` in that order.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
         <v>5</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>sets-and-dictionaries</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>dictionary-operations</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O2" t="b">
+      <c r="O32" t="b">
         <v>0</v>
       </c>
-      <c r="P2" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q2" t="b">
-        <v>1</v>
-      </c>
-      <c r="R2" t="inlineStr">
+      <c r="P32" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q32" t="b">
+        <v>1</v>
+      </c>
+      <c r="R32" t="inlineStr">
         <is>
           <t>a b a c b a</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="S32" t="inlineStr">
         <is>
           <t>a 3
 b 2
 c 1</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="T32" t="inlineStr">
         <is>
           <t>dog cat dog</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="U32" t="inlineStr">
         <is>
           <t>dog 2
 cat 1</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="V32" t="inlineStr">
         <is>
           <t>x y z</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="W32" t="inlineStr">
         <is>
           <t>x 1
 y 1
 z 1</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>solo</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Y32" t="inlineStr">
         <is>
           <t>solo 1</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="Z32" t="inlineStr">
         <is>
           <t>a a b b c c</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AA32" t="inlineStr">
         <is>
           <t>a 2
 b 2
 c 2</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AB32" t="inlineStr">
         <is>
           <t>z y x z y z</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AC32" t="inlineStr">
         <is>
           <t>z 3
 y 2
 x 1</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AD32" t="inlineStr">
         <is>
           <t>one two two three three three</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AE32" t="inlineStr">
         <is>
           <t>three 3
 two 2
 one 1</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AG32" t="inlineStr">
         <is>
           <t>words = input().split()
 counts = {}
 for w in words:
     counts[w] = counts.get(w, 0) + 1
-for w, c in sorted(counts.items(), key=lambda t: (-t[1], t[0])):
+for w, c in sorted(counts.items(), key=lambda t: (-t[1], t[0])):   # highest count first, ties broken alphabetically
     print(w, c)</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>Python - Character Frequency Ranking</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Read a word and print each character with its count as 'char:count', ordered by count from highest to lowest, breaking ties alphabetically.
-### Input Format
-- Line 1: A word
-### Output Format
-```
-l:2
-e:1
-h:1
-o:1
-```
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>A cryptography club practices basic frequency analysis before tackling real ciphers, starting with a simple exercise of counting how often each letter appears in a given word and ranking them from most to least frequent.
+Read a word and print each character with its count as 'char:count', ordered by count from highest to lowest, breaking ties alphabetically.
 ### Example Walkthrough
 In the sample, the word is `hello`. The letter `l` appears twice, more than any other character, so it is printed first as `l:2`, followed by the remaining letters `e`, `h`, and `o` (each appearing once) in alphabetical order.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
         <v>5</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>sets-and-dictionaries</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>dictionary-operations</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O3" t="b">
+      <c r="O33" t="b">
         <v>0</v>
       </c>
-      <c r="P3" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q3" t="b">
-        <v>1</v>
-      </c>
-      <c r="R3" t="inlineStr">
+      <c r="P33" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q33" t="b">
+        <v>1</v>
+      </c>
+      <c r="R33" t="inlineStr">
         <is>
           <t>hello</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S33" t="inlineStr">
         <is>
           <t>l:2
 e:1
@@ -6480,24 +5703,24 @@
 o:1</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="T33" t="inlineStr">
         <is>
           <t>aabbcc</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U33" t="inlineStr">
         <is>
           <t>a:2
 b:2
 c:2</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="V33" t="inlineStr">
         <is>
           <t>mississippi</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="W33" t="inlineStr">
         <is>
           <t>i:4
 s:4
@@ -6505,203 +5728,196 @@
 m:1</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="X33" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Y33" t="inlineStr">
         <is>
           <t>a:1</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="Z33" t="inlineStr">
         <is>
           <t>zzzzyyyxx</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AA33" t="inlineStr">
         <is>
           <t>z:4
 y:3
 x:2</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AB33" t="inlineStr">
         <is>
           <t>abcabcabc</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AC33" t="inlineStr">
         <is>
           <t>a:3
 b:3
 c:3</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AD33" t="inlineStr">
         <is>
           <t>banana</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AE33" t="inlineStr">
         <is>
           <t>a:3
 n:2
 b:1</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AG33" t="inlineStr">
         <is>
           <t>word = input()
 counts = {}
 for ch in word:
     counts[ch] = counts.get(ch, 0) + 1
-for ch, c in sorted(counts.items(), key=lambda t: (-t[1], t[0])):
+for ch, c in sorted(counts.items(), key=lambda t: (-t[1], t[0])):   # highest count first, ties broken alphabetically
     print(f"{ch}:{c}")</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>Python - Group by Length</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Read a sentence and group its words by length. For each length in ascending order, print 'length: ' followed by the words of that length in order of appearance, separated by spaces.
-### Input Format
-- Line 1: A sentence
-### Output Format
-```
-1: a
-3: cat dog
-4: fish bird
-```
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>For a hostel game night, the quiz master is preparing a word-guessing round and wants the shortlisted words grouped by their length, so shorter words can be used as easy clues and longer ones as tough clues.
+Read a sentence and group its words by length. For each length in ascending order, print 'length: ' followed by the words of that length in order of appearance, separated by spaces.
 ### Example Walkthrough
-In the sample, the sentence is `a cat dog fish bird`. Grouped by length, `a` has length `1`, `cat` and `dog` have length `3`, and `fish` and `bird` have length `4`, so the program prints `1: a`, `3: cat dog`, and `4: fish bird`.
+In the sample, the sentence is `cat dog fish bird a`. Grouped by length, `a` has length `1`, `cat` and `dog` have length `3`, and `fish` and `bird` have length `4`, so the program prints `1: a`, `3: cat dog`, and `4: fish bird`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
         <v>5</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>sets-and-dictionaries</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>dictionary-operations</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O4" t="b">
+      <c r="O34" t="b">
         <v>0</v>
       </c>
-      <c r="P4" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q4" t="b">
-        <v>1</v>
-      </c>
-      <c r="R4" t="inlineStr">
+      <c r="P34" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q34" t="b">
+        <v>1</v>
+      </c>
+      <c r="R34" t="inlineStr">
         <is>
           <t>cat dog fish bird a</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="S34" t="inlineStr">
         <is>
           <t>1: a
 3: cat dog
 4: fish bird</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="T34" t="inlineStr">
         <is>
           <t>hi hey</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="U34" t="inlineStr">
         <is>
           <t>2: hi
 3: hey</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="V34" t="inlineStr">
         <is>
           <t>one two six</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="W34" t="inlineStr">
         <is>
           <t>3: one two six</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="X34" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Y34" t="inlineStr">
         <is>
           <t>1: x</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="Z34" t="inlineStr">
         <is>
           <t>aa bb cc</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AA34" t="inlineStr">
         <is>
           <t>2: aa bb cc</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AB34" t="inlineStr">
         <is>
           <t>a bb ccc dddd eeeee</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AC34" t="inlineStr">
         <is>
           <t>1: a
 2: bb
@@ -6710,110 +5926,102 @@
 5: eeeee</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AD34" t="inlineStr">
         <is>
           <t>cat bat hat mat sat pat</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AE34" t="inlineStr">
         <is>
           <t>3: cat bat hat mat sat pat</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr">
+      <c r="AG34" t="inlineStr">
         <is>
           <t>words = input().split()
 groups = {}
 for w in words:
-    groups.setdefault(len(w), []).append(w)
+    groups.setdefault(len(w), []).append(w)   # start a new list the first time a length appears
 for length in sorted(groups):
     print(f"{length}: {' '.join(groups[length])}")</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>Python - Common Keys Summed</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Read two dictionaries of 'key value' pairs, sized `N` and `M`. For each key present in both, print 'key:sum' where sum adds the two values, with keys sorted alphabetically.
-### Input Format
-- Line 1: N
-- Next N lines: 'key value'
-- Then: M
-- Next M lines: 'key value'
-### Output Format
-```
-b:5
-```
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Two hostel wings each keep their own snack-expense record for the semester as category-to-amount pairs, and the treasurer needs to combine the records for categories both wings spent on, adding the amounts together.
+Read two dictionaries of 'key value' pairs, sized `N` and `M`. For each key present in both, print 'key:sum' where sum adds the two values, with keys sorted alphabetically.
 ### Example Walkthrough
 In the sample, the first dictionary has `a 1` and `b 2`, and the second has `b 3` and `c 4`. Only `b` is present in both, summing to `2 + 3 = 5`, so the program prints `b:5`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
         <v>5</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>sets-and-dictionaries</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>dictionary-operations</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O5" t="b">
+      <c r="O35" t="b">
         <v>0</v>
       </c>
-      <c r="P5" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" t="b">
-        <v>1</v>
-      </c>
-      <c r="R5" t="inlineStr">
+      <c r="P35" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q35" t="b">
+        <v>1</v>
+      </c>
+      <c r="R35" t="inlineStr">
         <is>
           <t>2
 a 1
@@ -6823,12 +6031,12 @@
 c 4</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="S35" t="inlineStr">
         <is>
           <t>b:5</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="T35" t="inlineStr">
         <is>
           <t>1
 x 5
@@ -6836,12 +6044,12 @@
 x 10</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="U35" t="inlineStr">
         <is>
           <t>x:15</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="V35" t="inlineStr">
         <is>
           <t>2
 p 1
@@ -6850,32 +6058,32 @@
 q 8</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="W35" t="inlineStr">
         <is>
           <t>q:10</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="X35" t="inlineStr">
         <is>
           <t>0
 0</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="Z35" t="inlineStr">
         <is>
           <t>1
 a 1
 0</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AB35" t="inlineStr">
         <is>
           <t>0
 1
 x 5</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AD35" t="inlineStr">
         <is>
           <t>3
 a 1
@@ -6887,14 +6095,14 @@
 c 30</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AE35" t="inlineStr">
         <is>
           <t>a:11
 b:22
 c:33</t>
         </is>
       </c>
-      <c r="AG5" t="inlineStr">
+      <c r="AG35" t="inlineStr">
         <is>
           <t>first = {}
 n = int(input())
@@ -6907,161 +6115,156 @@
     key, value = input().split()
     second[key] = int(value)
 for key in sorted(first):
-    if key in second:
+    if key in second:   # only keys present in both dictionaries
         print(f"{key}:{first[key] + second[key]}")</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>Python - Majority Element</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Read a line of space-separated numbers and print the value that appears more than half the time. If no value has a strict majority, print 'None'.
-### Input Format
-- Line 1: Space-separated numbers
-### Output Format
-```
-1
-```
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>In a college class representative election, votes are cast by the roll number of the candidate chosen, and the result is declared only if one candidate has won more than half of all the votes cast.
+Read a line of space-separated numbers and print the value that appears more than half the time. If no value has a strict majority, print 'None'.
 ### Example Walkthrough
 In the sample, the numbers are `1 1 1 2 3`. The value `1` appears `3` times out of `5`, more than half, so the program prints `1`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
         <v>5</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>sets-and-dictionaries</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>dictionary-operations</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O6" t="b">
+      <c r="O36" t="b">
         <v>0</v>
       </c>
-      <c r="P6" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q6" t="b">
-        <v>1</v>
-      </c>
-      <c r="R6" t="inlineStr">
+      <c r="P36" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q36" t="b">
+        <v>1</v>
+      </c>
+      <c r="R36" t="inlineStr">
         <is>
           <t>1 1 1 2 3</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="T36" t="inlineStr">
         <is>
           <t>1 2 3 4</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="U36" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="V36" t="inlineStr">
         <is>
           <t>2 2 2 2</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="W36" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="X36" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Y36" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="Z36" t="inlineStr">
         <is>
           <t>1 1 2 2 3</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AA36" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AB36" t="inlineStr">
         <is>
           <t>-1 -1 -1 -2</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AC36" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AD36" t="inlineStr">
         <is>
           <t>1 1 1 1 1 2 2 2 3 3</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AE36" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr">
+      <c r="AG36" t="inlineStr">
         <is>
           <t>nums = list(map(int, input().split()))
 counts = {}
@@ -7069,93 +6272,87 @@
     counts[x] = counts.get(x, 0) + 1
 answer = "None"
 for value, c in counts.items():
-    if c &gt; len(nums) / 2:
+    if c &gt; len(nums) / 2:   # majority means appearing more than half the time
         answer = value
 print(answer)</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>Python - Count Anagram Groups</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Read `N` words and print how many distinct anagram groups they form (words are in the same group if they use the same letters).
-### Input Format
-- Line 1: N
-- Next N lines: one word each
-### Output Format
-```
-2
-```
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>A spelling bee study group is sorting their practice word list into clusters of words that use exactly the same letters, since anagram pairs are a favorite trick question in the competition, and they want to know how many distinct groups their list forms.
+Read `N` words and print how many distinct anagram groups they form (words are in the same group if they use the same letters).
 ### Example Walkthrough
-In the sample, `N` is `3` with the words `cat`, `act`, and `dog`. `cat` and `act` use the same letters and form one group, while `dog` forms another, so the program prints `2`.
+In the sample, `N` is `3` with the words `listen`, `silent`, and `hello`. `listen` and `silent` use the same letters and form one group, while `hello` forms another, so the program prints `2`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
         <v>5</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>sets-and-dictionaries</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>sets</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O7" t="b">
+      <c r="O37" t="b">
         <v>0</v>
       </c>
-      <c r="P7" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q7" t="b">
-        <v>1</v>
-      </c>
-      <c r="R7" t="inlineStr">
+      <c r="P37" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q37" t="b">
+        <v>1</v>
+      </c>
+      <c r="R37" t="inlineStr">
         <is>
           <t>3
 listen
@@ -7163,24 +6360,24 @@
 hello</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="S37" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="T37" t="inlineStr">
         <is>
           <t>2
 abc
 cba</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="U37" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="V37" t="inlineStr">
         <is>
           <t>3
 cat
@@ -7188,33 +6385,33 @@
 bird</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="W37" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="X37" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Y37" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="Z37" t="inlineStr">
         <is>
           <t>1
 solo</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AA37" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AB37" t="inlineStr">
         <is>
           <t>4
 abc
@@ -7223,12 +6420,12 @@
 xyz</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AC37" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AD37" t="inlineStr">
         <is>
           <t>5
 rat
@@ -7238,103 +6435,96 @@
 arc</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AE37" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
+      <c r="AG37" t="inlineStr">
         <is>
           <t>n = int(input())
 groups = set()
 for _ in range(n):
     word = input()
-    groups.add("".join(sorted(word)))
+    groups.add("".join(sorted(word)))   # sorted letters are identical for anagrams
 print(len(groups))</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>Python - Top Customer</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>Read `N` transactions, each a customer name and an amount. Print the customer with the highest total spend. If several tie, print the name that comes first alphabetically.
-### Input Format
-- Line 1: N
-- Next N lines: 'name amount'
-### Output Format
-```
-asha
-```
 ### Example Walkthrough
 In the sample, `N` is `3` with `asha 100`, `kabir 50`, and `asha 80`. `asha`'s total is `100 + 80 = 180`, more than `kabir`'s `50`, so the program prints `asha`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
         <v>5</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>sets-and-dictionaries</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>dictionary-operations</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O8" t="b">
+      <c r="O38" t="b">
         <v>0</v>
       </c>
-      <c r="P8" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q8" t="b">
-        <v>1</v>
-      </c>
-      <c r="R8" t="inlineStr">
+      <c r="P38" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q38" t="b">
+        <v>1</v>
+      </c>
+      <c r="R38" t="inlineStr">
         <is>
           <t>4
 asha 100
@@ -7343,23 +6533,23 @@
 kabir 50</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="S38" t="inlineStr">
         <is>
           <t>asha</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="T38" t="inlineStr">
         <is>
           <t>1
 sam 5</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="U38" t="inlineStr">
         <is>
           <t>sam</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="V38" t="inlineStr">
         <is>
           <t>3
 a 10
@@ -7367,35 +6557,35 @@
 a 25</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="W38" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="X38" t="inlineStr">
         <is>
           <t>1
 solo 0</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Y38" t="inlineStr">
         <is>
           <t>solo</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="Z38" t="inlineStr">
         <is>
           <t>2
 a 0
 b 0</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AA38" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AB38" t="inlineStr">
         <is>
           <t>4
 x 10
@@ -7404,12 +6594,12 @@
 x 0</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AC38" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AD38" t="inlineStr">
         <is>
           <t>5
 p 100
@@ -7419,107 +6609,99 @@
 q 0</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AE38" t="inlineStr">
         <is>
           <t>p</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
+      <c r="AG38" t="inlineStr">
         <is>
           <t>n = int(input())
 totals = {}
 for _ in range(n):
     name, amount = input().split()
-    totals[name] = totals.get(name, 0) + int(amount)
-best = max(totals.values())
-winners = sorted(name for name, t in totals.items() if t == best)
+    totals[name] = totals.get(name, 0) + int(amount)   # accumulate spending per customer
+best = max(totals.values())   # highest total spent
+winners = sorted(name for name, t in totals.items() if t == best)   # alphabetical tie-break
 print(winners[0])</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>Python - Nested Marks Average</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>A report-card generator stores each student's marks in two tests inside a dictionary of dictionaries, keyed first by student name. When a name is queried, it prints that student's average of the two test marks, or `Not found` if the student wasn't recorded.
 Write a program that reads a whole number N, then reads N lines each with a name and two test marks separated by spaces and stores them in a nested dictionary, then reads one more name and prints the average of that student's two marks if found, or `Not found` otherwise.
-### Input Format
-- Line 1: N, the number of students
-- Next N lines: name, first mark, and second mark separated by spaces
-- Final line: the name being queried
-### Output Format
-```
-85.0
-```
 ### Example Walkthrough
 In the sample, N is 2 with `Asha 80 90` and `Rohan 70 75` recorded, and the query is `Asha`. Asha's average is (80 + 90) / 2 = 85.0, so the program prints `85.0`.
 ### Constraints
 - Names contain no spaces, and marks are valid whole numbers.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
         <v>5</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>sets-and-dictionaries</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>nested-dictionaries</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O9" t="b">
+      <c r="O39" t="b">
         <v>0</v>
       </c>
-      <c r="P9" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q9" t="b">
-        <v>1</v>
-      </c>
-      <c r="R9" t="inlineStr">
+      <c r="P39" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q39" t="b">
+        <v>1</v>
+      </c>
+      <c r="R39" t="inlineStr">
         <is>
           <t>2
 Asha 80 90
@@ -7527,24 +6709,24 @@
 Asha</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S39" t="inlineStr">
         <is>
           <t>85.0</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="T39" t="inlineStr">
         <is>
           <t>1
 Meena 100 50
 Meena</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="U39" t="inlineStr">
         <is>
           <t>75.0</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="V39" t="inlineStr">
         <is>
           <t>2
 A 1 3
@@ -7552,24 +6734,24 @@
 B</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="W39" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="X39" t="inlineStr">
         <is>
           <t>1
 X 0 0
 Y</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Y39" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="Z39" t="inlineStr">
         <is>
           <t>3
 D 10 20
@@ -7578,12 +6760,12 @@
 F</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AA39" t="inlineStr">
         <is>
           <t>55.0</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AB39" t="inlineStr">
         <is>
           <t>2
 P -10 10
@@ -7591,139 +6773,131 @@
 P</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AC39" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AD39" t="inlineStr">
         <is>
           <t>1
 S 99 100
 S</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AE39" t="inlineStr">
         <is>
           <t>99.5</t>
         </is>
       </c>
-      <c r="AG9" t="inlineStr">
+      <c r="AG39" t="inlineStr">
         <is>
           <t>n=int(input()); data={}
 for _ in range(n):
- name,m1,m2=input().split(); data[name]={"m1":int(m1),"m2":int(m2)}
-t=input(); print((data[t]["m1"]+data[t]["m2"])/2 if t in data else "Not found")</t>
+ name,m1,m2=input().split(); data[name]={"m1":int(m1),"m2":int(m2)}   # nested dict stores both marks per name
+t=input(); print((data[t]["m1"]+data[t]["m2"])/2 if t in data else "Not found")   # average the two marks if the name exists</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>Python - Invert Dictionary</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>A gift-shop inventory system stores each item's code mapped to its name. For a reverse-lookup screen, the system needs an inverted table that maps each name back to its code, sorted alphabetically by name. If two items share the same name, the code from the later entry overwrites the earlier one.
 Write a program that reads a whole number N, then reads N lines each with a code and a name separated by a space, builds an inverted dictionary mapping name to code, and prints each entry sorted alphabetically by name in the form `&lt;name&gt;:&lt;code&gt;`.
-### Input Format
-- Line 1: N, the number of items
-- Next N lines: code and name separated by a space
-### Output Format
-```
-1:a
-2:b
-```
 ### Example Walkthrough
 In the sample, N is 2 with `a 1` and `b 2`. Inverting gives `1` mapped to `a` and `2` mapped to `b`, and printing them sorted by name gives `1:a` then `2:b`.
 ### Constraints
 - Codes and names contain no spaces within them.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
         <v>5</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>sets-and-dictionaries</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>dictionary-operations</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O10" t="b">
+      <c r="O40" t="b">
         <v>0</v>
       </c>
-      <c r="P10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" t="b">
-        <v>1</v>
-      </c>
-      <c r="R10" t="inlineStr">
+      <c r="P40" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q40" t="b">
+        <v>1</v>
+      </c>
+      <c r="R40" t="inlineStr">
         <is>
           <t>2
 a 1
 b 2</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="S40" t="inlineStr">
         <is>
           <t>1:a
 2:b</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="T40" t="inlineStr">
         <is>
           <t>1
 x y</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U40" t="inlineStr">
         <is>
           <t>y:x</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="V40" t="inlineStr">
         <is>
           <t>3
 a red
@@ -7731,44 +6905,44 @@
 c green</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="W40" t="inlineStr">
         <is>
           <t>blue:b
 green:c
 red:a</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="X40" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="Z40" t="inlineStr">
         <is>
           <t>2
 name Asha
 city Pune</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AA40" t="inlineStr">
         <is>
           <t>Asha:name
 Pune:city</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AB40" t="inlineStr">
         <is>
           <t>2
 a 1
 b 1</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AC40" t="inlineStr">
         <is>
           <t>1:b</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AD40" t="inlineStr">
         <is>
           <t>4
 w 4
@@ -7777,7 +6951,7 @@
 z 1</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AE40" t="inlineStr">
         <is>
           <t>1:z
 2:y
@@ -7785,183 +6959,175 @@
 4:w</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr">
+      <c r="AG40" t="inlineStr">
         <is>
           <t>n=int(input()); d={}
 for _ in range(n):
- k,v=input().split(); d[v]=k
-for v in sorted(d): print(f"{v}:{d[v]}")</t>
+ k,v=input().split(); d[v]=k   # invert: store value as key, key as value
+for v in sorted(d): print(f"{v}:{d[v]}")   # print inverted pairs sorted by the new keys</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>Python - Membership Queries</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>An event check-in system keeps a set of names on the guest list. As people arrive one by one, the desk types out each visitor's name and needs an instant `Yes` or `No` for whether they're on the list.
 Write a program that reads a line of space-separated names into a set (the guest list), then reads a second line of space-separated names to check, and for each name checked prints `Yes` if it is in the guest list, or `No` otherwise, one result per line in the order checked.
-### Input Format
-- Line 1: Space-separated names (the guest list)
-- Line 2: Space-separated names (the names to check)
-### Output Format
-```
-Yes
-No
-```
 ### Example Walkthrough
 In the sample, the guest list is `a b c` and the names to check are `a d`. `a` is on the list, so it prints `Yes`; `d` is not, so it prints `No`.
 ### Constraints
 - The inputs are valid lines of space-separated names.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
         <v>5</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>sets-and-dictionaries</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>choosing-data-structures</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O11" t="b">
+      <c r="O41" t="b">
         <v>0</v>
       </c>
-      <c r="P11" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q11" t="b">
-        <v>1</v>
-      </c>
-      <c r="R11" t="inlineStr">
+      <c r="P41" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q41" t="b">
+        <v>1</v>
+      </c>
+      <c r="R41" t="inlineStr">
         <is>
           <t>a b c
 a d</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="S41" t="inlineStr">
         <is>
           <t>Yes
 No</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T41" t="inlineStr">
         <is>
           <t>1 2 3
 3 4</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U41" t="inlineStr">
         <is>
           <t>Yes
 No</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V41" t="inlineStr">
         <is>
           <t>x
 x</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="W41" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="X41" t="inlineStr">
         <is>
           <t>red blue
 green red</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Y41" t="inlineStr">
         <is>
           <t>No
 Yes</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="Z41" t="inlineStr">
         <is>
           <t>p
 a</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AA41" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AB41" t="inlineStr">
         <is>
           <t>p q
 q p r</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AC41" t="inlineStr">
         <is>
           <t>Yes
 Yes
 No</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AD41" t="inlineStr">
         <is>
           <t>5 5
 5 6</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AE41" t="inlineStr">
         <is>
           <t>Yes
 No</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>stored=set(input().split())
+      <c r="AG41" t="inlineStr">
+        <is>
+          <t>stored=set(input().split())   # set gives fast membership checks
 for q in input().split(): print("Yes" if q in stored else "No")</t>
         </is>
       </c>
